--- a/data/BerkData.xlsx
+++ b/data/BerkData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49BF3A1E-F914-4294-AFEC-3970F7D15BFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{49BF3A1E-F914-4294-AFEC-3970F7D15BFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8964E5BD-7E36-4277-83F7-2E9F7B4BA1ED}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="5940" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -1561,13 +1561,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E850A034-3729-4F84-81A0-F1DDCFD4FBCC}" name="Table1" displayName="Table1" ref="A1:L473" totalsRowShown="0">
-  <autoFilter ref="A1:L473" xr:uid="{E850A034-3729-4F84-81A0-F1DDCFD4FBCC}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Bilgisayar Mühendisliği"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:L473" xr:uid="{E850A034-3729-4F84-81A0-F1DDCFD4FBCC}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{769BB3A9-BC2D-4B0E-97B5-9CDAEEA9BFD5}" name="DepartmentName"/>
     <tableColumn id="2" xr3:uid="{C86EDC24-CDF3-487D-BE22-4DFF16AF6CEC}" name="CourseCode"/>
@@ -1850,21 +1844,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L473"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="46.7265625" customWidth="1"/>
-    <col min="2" max="2" width="22.81640625" customWidth="1"/>
-    <col min="3" max="3" width="27.26953125" customWidth="1"/>
-    <col min="4" max="4" width="13.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.1796875" customWidth="1"/>
-    <col min="8" max="8" width="11.453125" customWidth="1"/>
-    <col min="9" max="9" width="11.6328125" customWidth="1"/>
-    <col min="10" max="10" width="10.1796875" customWidth="1"/>
-    <col min="11" max="11" width="16.453125" customWidth="1"/>
-    <col min="12" max="12" width="13.7265625" customWidth="1"/>
+    <col min="1" max="1" width="46.73046875" customWidth="1"/>
+    <col min="2" max="2" width="22.796875" customWidth="1"/>
+    <col min="3" max="3" width="27.265625" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" customWidth="1"/>
+    <col min="6" max="6" width="11.19921875" customWidth="1"/>
+    <col min="8" max="8" width="11.46484375" customWidth="1"/>
+    <col min="9" max="9" width="11.59765625" customWidth="1"/>
+    <col min="10" max="10" width="10.19921875" customWidth="1"/>
+    <col min="11" max="11" width="16.46484375" customWidth="1"/>
+    <col min="12" max="12" width="13.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1902,7 +1896,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>492</v>
       </c>
@@ -1940,7 +1934,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>492</v>
       </c>
@@ -1978,7 +1972,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>492</v>
       </c>
@@ -2016,7 +2010,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -2054,7 +2048,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -2092,7 +2086,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -2130,7 +2124,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -2168,7 +2162,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -2206,7 +2200,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -2244,7 +2238,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -2282,7 +2276,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -2320,7 +2314,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -2358,7 +2352,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -2396,7 +2390,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -2434,7 +2428,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>492</v>
       </c>
@@ -2472,7 +2466,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>492</v>
       </c>
@@ -2510,7 +2504,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -2548,7 +2542,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -2586,7 +2580,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -2624,7 +2618,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -2662,7 +2656,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -2700,7 +2694,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>17</v>
       </c>
@@ -2738,7 +2732,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -2776,7 +2770,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -2814,7 +2808,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>32</v>
       </c>
@@ -2852,7 +2846,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>24</v>
       </c>
@@ -2890,7 +2884,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>24</v>
       </c>
@@ -2928,7 +2922,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>24</v>
       </c>
@@ -2966,7 +2960,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>24</v>
       </c>
@@ -3004,7 +2998,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -3042,7 +3036,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>24</v>
       </c>
@@ -3080,7 +3074,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>20</v>
       </c>
@@ -3118,7 +3112,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>20</v>
       </c>
@@ -3156,7 +3150,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>32</v>
       </c>
@@ -3194,7 +3188,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>27</v>
       </c>
@@ -3232,7 +3226,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>24</v>
       </c>
@@ -3270,7 +3264,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>24</v>
       </c>
@@ -3308,7 +3302,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>24</v>
       </c>
@@ -3346,7 +3340,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>24</v>
       </c>
@@ -3384,7 +3378,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>27</v>
       </c>
@@ -3422,7 +3416,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>27</v>
       </c>
@@ -3460,7 +3454,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>27</v>
       </c>
@@ -3498,7 +3492,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>20</v>
       </c>
@@ -3536,7 +3530,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>20</v>
       </c>
@@ -3574,7 +3568,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>20</v>
       </c>
@@ -3612,7 +3606,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>20</v>
       </c>
@@ -3650,7 +3644,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>27</v>
       </c>
@@ -3688,7 +3682,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>22</v>
       </c>
@@ -3726,7 +3720,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>17</v>
       </c>
@@ -3764,7 +3758,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>17</v>
       </c>
@@ -3802,7 +3796,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>24</v>
       </c>
@@ -3840,7 +3834,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>24</v>
       </c>
@@ -3878,7 +3872,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>22</v>
       </c>
@@ -3916,7 +3910,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>32</v>
       </c>
@@ -3954,7 +3948,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>20</v>
       </c>
@@ -3992,7 +3986,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>32</v>
       </c>
@@ -4030,7 +4024,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>24</v>
       </c>
@@ -4068,7 +4062,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -4106,7 +4100,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>24</v>
       </c>
@@ -4144,7 +4138,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>20</v>
       </c>
@@ -4182,7 +4176,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>32</v>
       </c>
@@ -4220,7 +4214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>32</v>
       </c>
@@ -4258,7 +4252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>32</v>
       </c>
@@ -4296,7 +4290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>32</v>
       </c>
@@ -4334,7 +4328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>32</v>
       </c>
@@ -4372,7 +4366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>32</v>
       </c>
@@ -4410,7 +4404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>32</v>
       </c>
@@ -4448,7 +4442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>32</v>
       </c>
@@ -4486,7 +4480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>32</v>
       </c>
@@ -4524,7 +4518,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>32</v>
       </c>
@@ -4562,7 +4556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>32</v>
       </c>
@@ -4600,7 +4594,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>32</v>
       </c>
@@ -4638,7 +4632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>27</v>
       </c>
@@ -4676,7 +4670,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>27</v>
       </c>
@@ -4714,7 +4708,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>27</v>
       </c>
@@ -4752,7 +4746,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>27</v>
       </c>
@@ -4790,7 +4784,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>27</v>
       </c>
@@ -4828,7 +4822,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>27</v>
       </c>
@@ -4866,7 +4860,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>27</v>
       </c>
@@ -4904,7 +4898,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>27</v>
       </c>
@@ -4942,7 +4936,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>27</v>
       </c>
@@ -4980,7 +4974,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>27</v>
       </c>
@@ -5018,7 +5012,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>27</v>
       </c>
@@ -5056,7 +5050,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>27</v>
       </c>
@@ -5094,7 +5088,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>27</v>
       </c>
@@ -5132,7 +5126,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>27</v>
       </c>
@@ -5170,7 +5164,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>17</v>
       </c>
@@ -5208,7 +5202,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>17</v>
       </c>
@@ -5246,7 +5240,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>17</v>
       </c>
@@ -5284,7 +5278,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>17</v>
       </c>
@@ -5322,7 +5316,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>17</v>
       </c>
@@ -5360,7 +5354,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>17</v>
       </c>
@@ -5398,7 +5392,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>17</v>
       </c>
@@ -5436,7 +5430,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>17</v>
       </c>
@@ -5474,7 +5468,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>17</v>
       </c>
@@ -5512,7 +5506,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>17</v>
       </c>
@@ -5550,7 +5544,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>17</v>
       </c>
@@ -5588,7 +5582,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>17</v>
       </c>
@@ -5626,7 +5620,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>17</v>
       </c>
@@ -5664,7 +5658,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>17</v>
       </c>
@@ -5702,7 +5696,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>17</v>
       </c>
@@ -5740,7 +5734,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>22</v>
       </c>
@@ -5778,7 +5772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>22</v>
       </c>
@@ -5816,7 +5810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>22</v>
       </c>
@@ -5854,7 +5848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>22</v>
       </c>
@@ -5892,7 +5886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>22</v>
       </c>
@@ -5930,7 +5924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>22</v>
       </c>
@@ -5968,7 +5962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>22</v>
       </c>
@@ -6006,7 +6000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>22</v>
       </c>
@@ -6044,7 +6038,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>17</v>
       </c>
@@ -6082,7 +6076,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>32</v>
       </c>
@@ -6120,7 +6114,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>24</v>
       </c>
@@ -6158,7 +6152,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>24</v>
       </c>
@@ -6196,7 +6190,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>17</v>
       </c>
@@ -6234,7 +6228,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>24</v>
       </c>
@@ -6272,7 +6266,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>24</v>
       </c>
@@ -6310,7 +6304,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>22</v>
       </c>
@@ -6348,7 +6342,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>492</v>
       </c>
@@ -6386,7 +6380,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>492</v>
       </c>
@@ -6424,7 +6418,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>32</v>
       </c>
@@ -6462,7 +6456,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>492</v>
       </c>
@@ -6500,7 +6494,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>492</v>
       </c>
@@ -6538,7 +6532,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>492</v>
       </c>
@@ -6576,7 +6570,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>492</v>
       </c>
@@ -6614,7 +6608,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>24</v>
       </c>
@@ -6652,7 +6646,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="127" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>24</v>
       </c>
@@ -6690,7 +6684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>20</v>
       </c>
@@ -6728,7 +6722,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="129" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>32</v>
       </c>
@@ -6766,7 +6760,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="130" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>32</v>
       </c>
@@ -6804,7 +6798,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>492</v>
       </c>
@@ -6842,7 +6836,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="132" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>27</v>
       </c>
@@ -6880,7 +6874,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="133" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>32</v>
       </c>
@@ -6918,7 +6912,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>492</v>
       </c>
@@ -6956,7 +6950,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="135" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>24</v>
       </c>
@@ -6994,7 +6988,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="136" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>24</v>
       </c>
@@ -7032,7 +7026,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="137" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>24</v>
       </c>
@@ -7070,7 +7064,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="138" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>24</v>
       </c>
@@ -7108,7 +7102,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="139" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>27</v>
       </c>
@@ -7146,7 +7140,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>492</v>
       </c>
@@ -7184,7 +7178,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="141" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>27</v>
       </c>
@@ -7222,7 +7216,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="142" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>20</v>
       </c>
@@ -7260,7 +7254,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="143" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>17</v>
       </c>
@@ -7298,7 +7292,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="144" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>24</v>
       </c>
@@ -7336,7 +7330,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="145" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>24</v>
       </c>
@@ -7374,7 +7368,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="146" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>24</v>
       </c>
@@ -7412,7 +7406,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="147" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>24</v>
       </c>
@@ -7450,7 +7444,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="148" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>27</v>
       </c>
@@ -7488,7 +7482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>24</v>
       </c>
@@ -7526,7 +7520,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="150" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>24</v>
       </c>
@@ -7564,7 +7558,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="151" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>24</v>
       </c>
@@ -7602,7 +7596,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="152" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>24</v>
       </c>
@@ -7640,7 +7634,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="153" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>24</v>
       </c>
@@ -7678,7 +7672,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="154" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>24</v>
       </c>
@@ -7716,7 +7710,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="155" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>27</v>
       </c>
@@ -7754,7 +7748,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="156" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>24</v>
       </c>
@@ -7792,7 +7786,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="157" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>24</v>
       </c>
@@ -7830,7 +7824,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="158" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>32</v>
       </c>
@@ -7868,7 +7862,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="159" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>20</v>
       </c>
@@ -7906,7 +7900,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="160" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>17</v>
       </c>
@@ -7944,7 +7938,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="161" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>27</v>
       </c>
@@ -7982,7 +7976,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="162" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>24</v>
       </c>
@@ -8020,7 +8014,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="163" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>24</v>
       </c>
@@ -8058,7 +8052,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="164" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>24</v>
       </c>
@@ -8096,7 +8090,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="165" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>24</v>
       </c>
@@ -8134,7 +8128,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>492</v>
       </c>
@@ -8172,7 +8166,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="167" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>27</v>
       </c>
@@ -8210,7 +8204,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="168" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>32</v>
       </c>
@@ -8248,7 +8242,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>17</v>
       </c>
@@ -8286,7 +8280,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="170" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>27</v>
       </c>
@@ -8324,7 +8318,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="171" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>20</v>
       </c>
@@ -8362,7 +8356,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="172" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>22</v>
       </c>
@@ -8400,7 +8394,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="173" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>20</v>
       </c>
@@ -8438,7 +8432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>27</v>
       </c>
@@ -8476,7 +8470,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="175" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>17</v>
       </c>
@@ -8514,7 +8508,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="176" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>24</v>
       </c>
@@ -8552,7 +8546,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="177" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>24</v>
       </c>
@@ -8590,7 +8584,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="178" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>32</v>
       </c>
@@ -8628,7 +8622,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
         <v>492</v>
       </c>
@@ -8666,7 +8660,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>492</v>
       </c>
@@ -8704,7 +8698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>492</v>
       </c>
@@ -8742,7 +8736,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="182" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>20</v>
       </c>
@@ -8780,7 +8774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>20</v>
       </c>
@@ -8818,7 +8812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>27</v>
       </c>
@@ -8856,7 +8850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>27</v>
       </c>
@@ -8894,7 +8888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
         <v>22</v>
       </c>
@@ -8932,7 +8926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>22</v>
       </c>
@@ -8970,7 +8964,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="188" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>17</v>
       </c>
@@ -9008,7 +9002,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="189" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
         <v>17</v>
       </c>
@@ -9046,7 +9040,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="190" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>17</v>
       </c>
@@ -9084,7 +9078,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="191" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>17</v>
       </c>
@@ -9122,7 +9116,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="192" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>17</v>
       </c>
@@ -9160,7 +9154,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="193" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
         <v>17</v>
       </c>
@@ -9198,7 +9192,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="194" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
         <v>17</v>
       </c>
@@ -9236,7 +9230,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="195" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
         <v>17</v>
       </c>
@@ -9274,7 +9268,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="196" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
         <v>17</v>
       </c>
@@ -9312,7 +9306,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="197" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
         <v>17</v>
       </c>
@@ -9350,7 +9344,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="198" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
         <v>20</v>
       </c>
@@ -9388,7 +9382,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="199" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
         <v>24</v>
       </c>
@@ -9426,7 +9420,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="200" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
         <v>24</v>
       </c>
@@ -9464,7 +9458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
         <v>24</v>
       </c>
@@ -9502,7 +9496,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="202" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
         <v>24</v>
       </c>
@@ -9540,7 +9534,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="203" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
         <v>24</v>
       </c>
@@ -9578,7 +9572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
         <v>24</v>
       </c>
@@ -9616,7 +9610,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="205" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
         <v>24</v>
       </c>
@@ -9654,7 +9648,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
         <v>24</v>
       </c>
@@ -9692,7 +9686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
         <v>24</v>
       </c>
@@ -9730,7 +9724,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="208" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
         <v>24</v>
       </c>
@@ -9768,7 +9762,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="209" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
         <v>24</v>
       </c>
@@ -9806,7 +9800,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="210" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
         <v>24</v>
       </c>
@@ -9844,7 +9838,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="211" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
         <v>24</v>
       </c>
@@ -9882,7 +9876,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="212" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A212" t="s">
         <v>24</v>
       </c>
@@ -9920,7 +9914,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="213" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A213" t="s">
         <v>27</v>
       </c>
@@ -9958,7 +9952,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="214" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A214" t="s">
         <v>27</v>
       </c>
@@ -9996,7 +9990,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="215" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
         <v>22</v>
       </c>
@@ -10034,7 +10028,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="216" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A216" t="s">
         <v>32</v>
       </c>
@@ -10072,7 +10066,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="217" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
         <v>27</v>
       </c>
@@ -10110,7 +10104,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="218" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
         <v>20</v>
       </c>
@@ -10148,7 +10142,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="219" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
         <v>32</v>
       </c>
@@ -10186,7 +10180,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
         <v>492</v>
       </c>
@@ -10224,7 +10218,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
         <v>492</v>
       </c>
@@ -10262,7 +10256,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
         <v>492</v>
       </c>
@@ -10300,7 +10294,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
         <v>492</v>
       </c>
@@ -10338,7 +10332,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
         <v>492</v>
       </c>
@@ -10376,7 +10370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
         <v>492</v>
       </c>
@@ -10414,7 +10408,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
         <v>492</v>
       </c>
@@ -10452,7 +10446,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="227" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A227" t="s">
         <v>24</v>
       </c>
@@ -10490,7 +10484,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="228" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A228" t="s">
         <v>24</v>
       </c>
@@ -10528,7 +10522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A229" t="s">
         <v>24</v>
       </c>
@@ -10566,7 +10560,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="230" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A230" t="s">
         <v>24</v>
       </c>
@@ -10604,7 +10598,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="231" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A231" t="s">
         <v>24</v>
       </c>
@@ -10642,7 +10636,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="232" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A232" t="s">
         <v>24</v>
       </c>
@@ -10680,7 +10674,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="233" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
         <v>27</v>
       </c>
@@ -10718,7 +10712,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="234" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A234" t="s">
         <v>27</v>
       </c>
@@ -10756,7 +10750,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
         <v>492</v>
       </c>
@@ -10794,7 +10788,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="236" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A236" t="s">
         <v>27</v>
       </c>
@@ -10832,7 +10826,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="237" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A237" t="s">
         <v>20</v>
       </c>
@@ -10870,7 +10864,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="238" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A238" t="s">
         <v>27</v>
       </c>
@@ -10908,7 +10902,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="239" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A239" t="s">
         <v>22</v>
       </c>
@@ -10946,7 +10940,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="240" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A240" t="s">
         <v>17</v>
       </c>
@@ -10984,7 +10978,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="241" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
         <v>20</v>
       </c>
@@ -11022,7 +11016,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="242" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A242" t="s">
         <v>17</v>
       </c>
@@ -11060,7 +11054,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="243" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A243" t="s">
         <v>20</v>
       </c>
@@ -11098,7 +11092,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="244" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
         <v>32</v>
       </c>
@@ -11136,7 +11130,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="245" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A245" t="s">
         <v>27</v>
       </c>
@@ -11174,7 +11168,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="246" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A246" t="s">
         <v>27</v>
       </c>
@@ -11212,7 +11206,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="247" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A247" t="s">
         <v>22</v>
       </c>
@@ -11250,7 +11244,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="248" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A248" t="s">
         <v>22</v>
       </c>
@@ -11288,7 +11282,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="249" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
         <v>22</v>
       </c>
@@ -11326,7 +11320,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="250" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
         <v>17</v>
       </c>
@@ -11364,7 +11358,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A251" t="s">
         <v>492</v>
       </c>
@@ -11402,7 +11396,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="252" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A252" t="s">
         <v>20</v>
       </c>
@@ -11440,7 +11434,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="253" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
         <v>32</v>
       </c>
@@ -11478,7 +11472,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="254" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A254" t="s">
         <v>17</v>
       </c>
@@ -11516,7 +11510,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="255" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A255" t="s">
         <v>27</v>
       </c>
@@ -11554,7 +11548,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="256" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A256" t="s">
         <v>22</v>
       </c>
@@ -11592,7 +11586,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="257" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A257" t="s">
         <v>20</v>
       </c>
@@ -11630,7 +11624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A258" t="s">
         <v>20</v>
       </c>
@@ -11668,7 +11662,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
         <v>492</v>
       </c>
@@ -11706,7 +11700,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="260" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A260" t="s">
         <v>24</v>
       </c>
@@ -11744,7 +11738,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="261" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A261" t="s">
         <v>24</v>
       </c>
@@ -11782,7 +11776,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="262" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
         <v>20</v>
       </c>
@@ -11820,7 +11814,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="263" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A263" t="s">
         <v>27</v>
       </c>
@@ -11858,7 +11852,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="264" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A264" t="s">
         <v>22</v>
       </c>
@@ -11896,7 +11890,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="265" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
         <v>22</v>
       </c>
@@ -11934,7 +11928,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="266" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A266" t="s">
         <v>27</v>
       </c>
@@ -11972,7 +11966,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="267" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A267" t="s">
         <v>27</v>
       </c>
@@ -12010,7 +12004,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="268" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
         <v>27</v>
       </c>
@@ -12048,7 +12042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A269" t="s">
         <v>20</v>
       </c>
@@ -12086,7 +12080,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="270" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A270" t="s">
         <v>22</v>
       </c>
@@ -12124,7 +12118,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="271" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
         <v>27</v>
       </c>
@@ -12162,7 +12156,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="272" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A272" t="s">
         <v>17</v>
       </c>
@@ -12200,7 +12194,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A273" t="s">
         <v>492</v>
       </c>
@@ -12238,7 +12232,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="274" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A274" t="s">
         <v>32</v>
       </c>
@@ -12276,7 +12270,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="275" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A275" t="s">
         <v>24</v>
       </c>
@@ -12314,7 +12308,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="276" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A276" t="s">
         <v>24</v>
       </c>
@@ -12352,7 +12346,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="277" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A277" t="s">
         <v>27</v>
       </c>
@@ -12390,7 +12384,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="278" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A278" t="s">
         <v>27</v>
       </c>
@@ -12428,7 +12422,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="279" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A279" t="s">
         <v>22</v>
       </c>
@@ -12466,7 +12460,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="280" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
         <v>24</v>
       </c>
@@ -12504,7 +12498,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="281" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A281" t="s">
         <v>24</v>
       </c>
@@ -12542,7 +12536,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="282" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A282" t="s">
         <v>24</v>
       </c>
@@ -12580,7 +12574,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="283" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A283" t="s">
         <v>24</v>
       </c>
@@ -12618,7 +12612,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="284" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A284" t="s">
         <v>24</v>
       </c>
@@ -12656,7 +12650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A285" t="s">
         <v>24</v>
       </c>
@@ -12694,7 +12688,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="286" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A286" t="s">
         <v>24</v>
       </c>
@@ -12732,7 +12726,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="287" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A287" t="s">
         <v>24</v>
       </c>
@@ -12770,7 +12764,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="288" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A288" t="s">
         <v>24</v>
       </c>
@@ -12808,7 +12802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
         <v>24</v>
       </c>
@@ -12846,7 +12840,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="290" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A290" t="s">
         <v>24</v>
       </c>
@@ -12884,7 +12878,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="291" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A291" t="s">
         <v>24</v>
       </c>
@@ -12922,7 +12916,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="292" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A292" t="s">
         <v>24</v>
       </c>
@@ -12960,7 +12954,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="293" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A293" t="s">
         <v>24</v>
       </c>
@@ -12998,7 +12992,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="294" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A294" t="s">
         <v>24</v>
       </c>
@@ -13036,7 +13030,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A295" t="s">
         <v>492</v>
       </c>
@@ -13074,7 +13068,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="296" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A296" t="s">
         <v>24</v>
       </c>
@@ -13112,7 +13106,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="297" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A297" t="s">
         <v>24</v>
       </c>
@@ -13150,7 +13144,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="298" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
         <v>24</v>
       </c>
@@ -13188,7 +13182,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="299" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A299" t="s">
         <v>24</v>
       </c>
@@ -13226,7 +13220,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="300" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A300" t="s">
         <v>20</v>
       </c>
@@ -13264,7 +13258,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="301" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A301" t="s">
         <v>22</v>
       </c>
@@ -13302,7 +13296,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A302" t="s">
         <v>492</v>
       </c>
@@ -13340,7 +13334,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="303" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A303" t="s">
         <v>17</v>
       </c>
@@ -13378,7 +13372,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="304" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A304" t="s">
         <v>20</v>
       </c>
@@ -13416,7 +13410,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="305" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A305" t="s">
         <v>27</v>
       </c>
@@ -13454,7 +13448,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="306" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A306" t="s">
         <v>27</v>
       </c>
@@ -13492,7 +13486,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="307" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
         <v>27</v>
       </c>
@@ -13530,7 +13524,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="308" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A308" t="s">
         <v>20</v>
       </c>
@@ -13568,7 +13562,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="309" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A309" t="s">
         <v>20</v>
       </c>
@@ -13606,7 +13600,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="310" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A310" t="s">
         <v>32</v>
       </c>
@@ -13644,7 +13638,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="311" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A311" t="s">
         <v>22</v>
       </c>
@@ -13682,7 +13676,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="312" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A312" t="s">
         <v>17</v>
       </c>
@@ -13720,7 +13714,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="313" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
         <v>27</v>
       </c>
@@ -13758,7 +13752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A314" t="s">
         <v>24</v>
       </c>
@@ -13796,7 +13790,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="315" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A315" t="s">
         <v>24</v>
       </c>
@@ -13834,7 +13828,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A316" t="s">
         <v>492</v>
       </c>
@@ -13872,7 +13866,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A317" t="s">
         <v>492</v>
       </c>
@@ -13910,7 +13904,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="318" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A318" t="s">
         <v>20</v>
       </c>
@@ -13948,7 +13942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A319" t="s">
         <v>20</v>
       </c>
@@ -13986,7 +13980,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="320" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A320" t="s">
         <v>20</v>
       </c>
@@ -14024,7 +14018,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="321" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A321" t="s">
         <v>27</v>
       </c>
@@ -14062,7 +14056,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="322" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A322" t="s">
         <v>27</v>
       </c>
@@ -14100,7 +14094,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="323" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A323" t="s">
         <v>27</v>
       </c>
@@ -14138,7 +14132,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="324" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A324" t="s">
         <v>24</v>
       </c>
@@ -14176,7 +14170,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="325" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
         <v>24</v>
       </c>
@@ -14214,7 +14208,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="326" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A326" t="s">
         <v>17</v>
       </c>
@@ -14252,7 +14246,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="327" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A327" t="s">
         <v>17</v>
       </c>
@@ -14290,7 +14284,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="328" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A328" t="s">
         <v>24</v>
       </c>
@@ -14328,7 +14322,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="329" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A329" t="s">
         <v>24</v>
       </c>
@@ -14366,7 +14360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A330" t="s">
         <v>492</v>
       </c>
@@ -14404,7 +14398,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A331" t="s">
         <v>492</v>
       </c>
@@ -14442,7 +14436,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="332" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A332" t="s">
         <v>20</v>
       </c>
@@ -14480,7 +14474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A333" t="s">
         <v>20</v>
       </c>
@@ -14518,7 +14512,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="334" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A334" t="s">
         <v>20</v>
       </c>
@@ -14556,7 +14550,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="335" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A335" t="s">
         <v>27</v>
       </c>
@@ -14594,7 +14588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A336" t="s">
         <v>27</v>
       </c>
@@ -14632,7 +14626,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="337" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A337" t="s">
         <v>27</v>
       </c>
@@ -14670,7 +14664,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="338" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A338" t="s">
         <v>24</v>
       </c>
@@ -14708,7 +14702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A339" t="s">
         <v>24</v>
       </c>
@@ -14746,7 +14740,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="340" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A340" t="s">
         <v>24</v>
       </c>
@@ -14784,7 +14778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="341" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A341" t="s">
         <v>17</v>
       </c>
@@ -14822,7 +14816,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="342" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A342" t="s">
         <v>17</v>
       </c>
@@ -14860,7 +14854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="343" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A343" t="s">
         <v>17</v>
       </c>
@@ -14898,7 +14892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A344" t="s">
         <v>17</v>
       </c>
@@ -14936,7 +14930,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="345" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A345" t="s">
         <v>492</v>
       </c>
@@ -14974,7 +14968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A346" t="s">
         <v>24</v>
       </c>
@@ -15012,7 +15006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A347" t="s">
         <v>492</v>
       </c>
@@ -15050,7 +15044,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="348" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A348" t="s">
         <v>17</v>
       </c>
@@ -15088,7 +15082,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="349" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A349" t="s">
         <v>492</v>
       </c>
@@ -15126,7 +15120,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="350" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A350" t="s">
         <v>32</v>
       </c>
@@ -15164,7 +15158,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="351" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A351" t="s">
         <v>24</v>
       </c>
@@ -15202,7 +15196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="352" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A352" t="s">
         <v>24</v>
       </c>
@@ -15240,7 +15234,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="353" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A353" t="s">
         <v>24</v>
       </c>
@@ -15278,7 +15272,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="354" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A354" t="s">
         <v>492</v>
       </c>
@@ -15316,7 +15310,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="355" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A355" t="s">
         <v>24</v>
       </c>
@@ -15354,7 +15348,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="356" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A356" t="s">
         <v>24</v>
       </c>
@@ -15392,7 +15386,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="357" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A357" t="s">
         <v>24</v>
       </c>
@@ -15430,7 +15424,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="358" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A358" t="s">
         <v>24</v>
       </c>
@@ -15468,7 +15462,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="359" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A359" t="s">
         <v>24</v>
       </c>
@@ -15506,7 +15500,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="360" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A360" t="s">
         <v>24</v>
       </c>
@@ -15544,7 +15538,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="361" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
         <v>24</v>
       </c>
@@ -15582,7 +15576,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="362" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A362" t="s">
         <v>24</v>
       </c>
@@ -15620,7 +15614,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="363" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A363" t="s">
         <v>24</v>
       </c>
@@ -15658,7 +15652,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="364" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A364" t="s">
         <v>24</v>
       </c>
@@ -15696,7 +15690,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="365" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A365" t="s">
         <v>492</v>
       </c>
@@ -15734,7 +15728,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="366" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A366" t="s">
         <v>17</v>
       </c>
@@ -15772,7 +15766,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="367" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A367" t="s">
         <v>24</v>
       </c>
@@ -15810,7 +15804,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="368" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A368" t="s">
         <v>24</v>
       </c>
@@ -15848,7 +15842,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="369" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A369" t="s">
         <v>17</v>
       </c>
@@ -15886,7 +15880,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="370" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A370" t="s">
         <v>492</v>
       </c>
@@ -15924,7 +15918,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="371" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A371" t="s">
         <v>27</v>
       </c>
@@ -15962,7 +15956,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="372" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A372" t="s">
         <v>22</v>
       </c>
@@ -16000,7 +15994,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="373" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A373" t="s">
         <v>27</v>
       </c>
@@ -16038,7 +16032,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="374" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A374" t="s">
         <v>32</v>
       </c>
@@ -16076,7 +16070,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="375" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A375" t="s">
         <v>22</v>
       </c>
@@ -16114,7 +16108,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="376" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A376" t="s">
         <v>24</v>
       </c>
@@ -16152,7 +16146,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="377" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A377" t="s">
         <v>24</v>
       </c>
@@ -16190,7 +16184,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="378" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A378" t="s">
         <v>492</v>
       </c>
@@ -16228,7 +16222,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="379" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A379" t="s">
         <v>24</v>
       </c>
@@ -16266,7 +16260,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="380" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A380" t="s">
         <v>24</v>
       </c>
@@ -16304,7 +16298,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="381" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A381" t="s">
         <v>492</v>
       </c>
@@ -16342,7 +16336,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="382" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A382" t="s">
         <v>27</v>
       </c>
@@ -16380,7 +16374,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="383" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A383" t="s">
         <v>27</v>
       </c>
@@ -16418,7 +16412,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="384" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A384" t="s">
         <v>27</v>
       </c>
@@ -16456,7 +16450,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="385" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A385" t="s">
         <v>27</v>
       </c>
@@ -16494,7 +16488,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="386" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A386" t="s">
         <v>27</v>
       </c>
@@ -16532,7 +16526,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="387" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A387" t="s">
         <v>27</v>
       </c>
@@ -16570,7 +16564,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="388" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A388" t="s">
         <v>27</v>
       </c>
@@ -16608,7 +16602,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="389" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A389" t="s">
         <v>27</v>
       </c>
@@ -16646,7 +16640,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="390" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A390" t="s">
         <v>27</v>
       </c>
@@ -16684,7 +16678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="391" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A391" t="s">
         <v>27</v>
       </c>
@@ -16722,7 +16716,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="392" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A392" t="s">
         <v>27</v>
       </c>
@@ -16760,7 +16754,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="393" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A393" t="s">
         <v>27</v>
       </c>
@@ -16798,7 +16792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="394" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A394" t="s">
         <v>27</v>
       </c>
@@ -16836,7 +16830,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="395" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A395" t="s">
         <v>27</v>
       </c>
@@ -16874,7 +16868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="396" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A396" t="s">
         <v>492</v>
       </c>
@@ -16912,7 +16906,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="397" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A397" t="s">
         <v>492</v>
       </c>
@@ -16950,7 +16944,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="398" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A398" t="s">
         <v>492</v>
       </c>
@@ -16988,7 +16982,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="399" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A399" t="s">
         <v>492</v>
       </c>
@@ -17026,7 +17020,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="400" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A400" t="s">
         <v>492</v>
       </c>
@@ -17064,7 +17058,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="401" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A401" t="s">
         <v>492</v>
       </c>
@@ -17102,7 +17096,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="402" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A402" t="s">
         <v>492</v>
       </c>
@@ -17140,7 +17134,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="403" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A403" t="s">
         <v>492</v>
       </c>
@@ -17178,7 +17172,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="404" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A404" t="s">
         <v>492</v>
       </c>
@@ -17216,7 +17210,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="405" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A405" t="s">
         <v>492</v>
       </c>
@@ -17254,7 +17248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="406" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A406" t="s">
         <v>20</v>
       </c>
@@ -17292,7 +17286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="407" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A407" t="s">
         <v>20</v>
       </c>
@@ -17330,7 +17324,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="408" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A408" t="s">
         <v>20</v>
       </c>
@@ -17368,7 +17362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="409" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A409" t="s">
         <v>27</v>
       </c>
@@ -17406,7 +17400,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="410" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A410" t="s">
         <v>27</v>
       </c>
@@ -17444,7 +17438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="411" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A411" t="s">
         <v>24</v>
       </c>
@@ -17482,7 +17476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="412" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A412" t="s">
         <v>24</v>
       </c>
@@ -17520,7 +17514,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="413" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A413" t="s">
         <v>24</v>
       </c>
@@ -17558,7 +17552,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="414" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A414" t="s">
         <v>17</v>
       </c>
@@ -17596,7 +17590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A415" t="s">
         <v>17</v>
       </c>
@@ -17634,7 +17628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="416" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A416" t="s">
         <v>24</v>
       </c>
@@ -17672,7 +17666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="417" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A417" t="s">
         <v>492</v>
       </c>
@@ -17710,7 +17704,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="418" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A418" t="s">
         <v>492</v>
       </c>
@@ -17748,7 +17742,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="419" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A419" t="s">
         <v>492</v>
       </c>
@@ -17786,7 +17780,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="420" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A420" t="s">
         <v>17</v>
       </c>
@@ -17824,7 +17818,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="421" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A421" t="s">
         <v>20</v>
       </c>
@@ -17862,7 +17856,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="422" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A422" t="s">
         <v>27</v>
       </c>
@@ -17900,7 +17894,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="423" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A423" t="s">
         <v>20</v>
       </c>
@@ -17938,7 +17932,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="424" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A424" t="s">
         <v>27</v>
       </c>
@@ -17976,7 +17970,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="425" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A425" t="s">
         <v>32</v>
       </c>
@@ -18014,7 +18008,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="426" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A426" t="s">
         <v>22</v>
       </c>
@@ -18052,7 +18046,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="427" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A427" t="s">
         <v>20</v>
       </c>
@@ -18090,7 +18084,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="428" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A428" t="s">
         <v>20</v>
       </c>
@@ -18128,7 +18122,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="429" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A429" t="s">
         <v>17</v>
       </c>
@@ -18166,7 +18160,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="430" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A430" t="s">
         <v>27</v>
       </c>
@@ -18204,7 +18198,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="431" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A431" t="s">
         <v>32</v>
       </c>
@@ -18242,7 +18236,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="432" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A432" t="s">
         <v>27</v>
       </c>
@@ -18280,7 +18274,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="433" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
         <v>17</v>
       </c>
@@ -18318,7 +18312,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="434" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A434" t="s">
         <v>17</v>
       </c>
@@ -18356,7 +18350,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="435" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A435" t="s">
         <v>27</v>
       </c>
@@ -18394,7 +18388,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="436" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A436" t="s">
         <v>20</v>
       </c>
@@ -18432,7 +18426,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="437" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A437" t="s">
         <v>17</v>
       </c>
@@ -18470,7 +18464,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="438" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A438" t="s">
         <v>492</v>
       </c>
@@ -18508,7 +18502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="439" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A439" t="s">
         <v>20</v>
       </c>
@@ -18546,7 +18540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="440" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A440" t="s">
         <v>27</v>
       </c>
@@ -18584,7 +18578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="441" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A441" t="s">
         <v>32</v>
       </c>
@@ -18622,7 +18616,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="442" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A442" t="s">
         <v>17</v>
       </c>
@@ -18660,7 +18654,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="443" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A443" t="s">
         <v>27</v>
       </c>
@@ -18698,7 +18692,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="444" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A444" t="s">
         <v>32</v>
       </c>
@@ -18736,7 +18730,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="445" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A445" t="s">
         <v>492</v>
       </c>
@@ -18774,7 +18768,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="446" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A446" t="s">
         <v>20</v>
       </c>
@@ -18812,7 +18806,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="447" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A447" t="s">
         <v>20</v>
       </c>
@@ -18850,7 +18844,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="448" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A448" t="s">
         <v>492</v>
       </c>
@@ -18888,7 +18882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="449" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A449" t="s">
         <v>492</v>
       </c>
@@ -18926,7 +18920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="450" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A450" t="s">
         <v>492</v>
       </c>
@@ -18964,7 +18958,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="451" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A451" t="s">
         <v>20</v>
       </c>
@@ -19002,7 +18996,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="452" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A452" t="s">
         <v>32</v>
       </c>
@@ -19040,7 +19034,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="453" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A453" t="s">
         <v>27</v>
       </c>
@@ -19078,7 +19072,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="454" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A454" t="s">
         <v>22</v>
       </c>
@@ -19116,7 +19110,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="455" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A455" t="s">
         <v>24</v>
       </c>
@@ -19154,7 +19148,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="456" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A456" t="s">
         <v>17</v>
       </c>
@@ -19192,7 +19186,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="457" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A457" t="s">
         <v>24</v>
       </c>
@@ -19230,7 +19224,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="458" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A458" t="s">
         <v>22</v>
       </c>
@@ -19268,7 +19262,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="459" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A459" t="s">
         <v>17</v>
       </c>
@@ -19306,7 +19300,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="460" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A460" t="s">
         <v>24</v>
       </c>
@@ -19344,7 +19338,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="461" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A461" t="s">
         <v>24</v>
       </c>
@@ -19382,7 +19376,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="462" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A462" t="s">
         <v>20</v>
       </c>
@@ -19420,7 +19414,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="463" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A463" t="s">
         <v>32</v>
       </c>
@@ -19458,7 +19452,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="464" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A464" t="s">
         <v>17</v>
       </c>
@@ -19496,7 +19490,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="465" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A465" t="s">
         <v>27</v>
       </c>
@@ -19534,7 +19528,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="466" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A466" t="s">
         <v>20</v>
       </c>
@@ -19572,7 +19566,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="467" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A467" t="s">
         <v>20</v>
       </c>
@@ -19610,7 +19604,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="468" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A468" t="s">
         <v>20</v>
       </c>
@@ -19648,7 +19642,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="469" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A469" t="s">
         <v>22</v>
       </c>
@@ -19686,7 +19680,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="470" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A470" t="s">
         <v>20</v>
       </c>
@@ -19724,7 +19718,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="471" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A471" t="s">
         <v>20</v>
       </c>
@@ -19762,7 +19756,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="472" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A472" t="s">
         <v>22</v>
       </c>
@@ -19800,7 +19794,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="473" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A473" t="s">
         <v>20</v>
       </c>

--- a/data/BerkData.xlsx
+++ b/data/BerkData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{49BF3A1E-F914-4294-AFEC-3970F7D15BFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8964E5BD-7E36-4277-83F7-2E9F7B4BA1ED}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD24A85-5295-4702-B5EB-B6C1668D4A66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -1561,7 +1561,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E850A034-3729-4F84-81A0-F1DDCFD4FBCC}" name="Table1" displayName="Table1" ref="A1:L473" totalsRowShown="0">
-  <autoFilter ref="A1:L473" xr:uid="{E850A034-3729-4F84-81A0-F1DDCFD4FBCC}"/>
+  <autoFilter ref="A1:L473" xr:uid="{E850A034-3729-4F84-81A0-F1DDCFD4FBCC}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="İnşaat Mühendisliği"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{769BB3A9-BC2D-4B0E-97B5-9CDAEEA9BFD5}" name="DepartmentName"/>
     <tableColumn id="2" xr3:uid="{C86EDC24-CDF3-487D-BE22-4DFF16AF6CEC}" name="CourseCode"/>
@@ -1844,21 +1850,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L473"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="46.73046875" customWidth="1"/>
-    <col min="2" max="2" width="22.796875" customWidth="1"/>
-    <col min="3" max="3" width="27.265625" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" customWidth="1"/>
-    <col min="6" max="6" width="11.19921875" customWidth="1"/>
-    <col min="8" max="8" width="11.46484375" customWidth="1"/>
-    <col min="9" max="9" width="11.59765625" customWidth="1"/>
-    <col min="10" max="10" width="10.19921875" customWidth="1"/>
-    <col min="11" max="11" width="16.46484375" customWidth="1"/>
-    <col min="12" max="12" width="13.73046875" customWidth="1"/>
+    <col min="1" max="1" width="46.7265625" customWidth="1"/>
+    <col min="2" max="2" width="22.81640625" customWidth="1"/>
+    <col min="3" max="3" width="27.26953125" customWidth="1"/>
+    <col min="4" max="4" width="13.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.1796875" customWidth="1"/>
+    <col min="8" max="8" width="11.453125" customWidth="1"/>
+    <col min="9" max="9" width="11.6328125" customWidth="1"/>
+    <col min="10" max="10" width="10.1796875" customWidth="1"/>
+    <col min="11" max="11" width="16.453125" customWidth="1"/>
+    <col min="12" max="12" width="13.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1896,7 +1902,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>492</v>
       </c>
@@ -1934,7 +1940,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>492</v>
       </c>
@@ -1972,7 +1978,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>492</v>
       </c>
@@ -2010,7 +2016,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -2048,7 +2054,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -2086,7 +2092,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -2124,7 +2130,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -2162,7 +2168,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -2200,7 +2206,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -2238,7 +2244,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -2276,7 +2282,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -2314,7 +2320,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -2352,7 +2358,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -2390,7 +2396,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -2428,7 +2434,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>492</v>
       </c>
@@ -2466,7 +2472,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>492</v>
       </c>
@@ -2504,7 +2510,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -2542,7 +2548,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -2580,7 +2586,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -2618,7 +2624,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -2656,7 +2662,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -2694,7 +2700,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>17</v>
       </c>
@@ -2732,7 +2738,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -2770,7 +2776,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -2808,7 +2814,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>32</v>
       </c>
@@ -2846,7 +2852,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>24</v>
       </c>
@@ -2884,7 +2890,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>24</v>
       </c>
@@ -2922,7 +2928,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>24</v>
       </c>
@@ -2960,7 +2966,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>24</v>
       </c>
@@ -2998,7 +3004,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -3036,7 +3042,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>24</v>
       </c>
@@ -3074,7 +3080,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>20</v>
       </c>
@@ -3112,7 +3118,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>20</v>
       </c>
@@ -3150,7 +3156,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>32</v>
       </c>
@@ -3188,7 +3194,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>27</v>
       </c>
@@ -3226,7 +3232,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>24</v>
       </c>
@@ -3264,7 +3270,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>24</v>
       </c>
@@ -3302,7 +3308,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>24</v>
       </c>
@@ -3340,7 +3346,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>24</v>
       </c>
@@ -3378,7 +3384,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>27</v>
       </c>
@@ -3416,7 +3422,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>27</v>
       </c>
@@ -3454,7 +3460,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>27</v>
       </c>
@@ -3492,7 +3498,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>20</v>
       </c>
@@ -3530,7 +3536,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>20</v>
       </c>
@@ -3568,7 +3574,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>20</v>
       </c>
@@ -3606,7 +3612,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>20</v>
       </c>
@@ -3644,7 +3650,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>27</v>
       </c>
@@ -3682,7 +3688,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>22</v>
       </c>
@@ -3720,7 +3726,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>17</v>
       </c>
@@ -3758,7 +3764,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>17</v>
       </c>
@@ -3796,7 +3802,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>24</v>
       </c>
@@ -3834,7 +3840,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>24</v>
       </c>
@@ -3872,7 +3878,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>22</v>
       </c>
@@ -3910,7 +3916,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>32</v>
       </c>
@@ -3948,7 +3954,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>20</v>
       </c>
@@ -3986,7 +3992,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>32</v>
       </c>
@@ -4024,7 +4030,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>24</v>
       </c>
@@ -4062,7 +4068,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -4100,7 +4106,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>24</v>
       </c>
@@ -4138,7 +4144,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>20</v>
       </c>
@@ -4176,7 +4182,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>32</v>
       </c>
@@ -4214,7 +4220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>32</v>
       </c>
@@ -4252,7 +4258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>32</v>
       </c>
@@ -4290,7 +4296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>32</v>
       </c>
@@ -4328,7 +4334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>32</v>
       </c>
@@ -4366,7 +4372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>32</v>
       </c>
@@ -4404,7 +4410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>32</v>
       </c>
@@ -4442,7 +4448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>32</v>
       </c>
@@ -4480,7 +4486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>32</v>
       </c>
@@ -4518,7 +4524,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>32</v>
       </c>
@@ -4556,7 +4562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>32</v>
       </c>
@@ -4594,7 +4600,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>32</v>
       </c>
@@ -4632,7 +4638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>27</v>
       </c>
@@ -4670,7 +4676,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>27</v>
       </c>
@@ -4708,7 +4714,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>27</v>
       </c>
@@ -4746,7 +4752,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>27</v>
       </c>
@@ -4784,7 +4790,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>27</v>
       </c>
@@ -4822,7 +4828,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>27</v>
       </c>
@@ -4860,7 +4866,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>27</v>
       </c>
@@ -4898,7 +4904,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>27</v>
       </c>
@@ -4936,7 +4942,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>27</v>
       </c>
@@ -4974,7 +4980,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>27</v>
       </c>
@@ -5012,7 +5018,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>27</v>
       </c>
@@ -5050,7 +5056,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>27</v>
       </c>
@@ -5088,7 +5094,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>27</v>
       </c>
@@ -5126,7 +5132,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>27</v>
       </c>
@@ -5164,7 +5170,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>17</v>
       </c>
@@ -5202,7 +5208,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>17</v>
       </c>
@@ -5240,7 +5246,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>17</v>
       </c>
@@ -5278,7 +5284,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>17</v>
       </c>
@@ -5316,7 +5322,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>17</v>
       </c>
@@ -5354,7 +5360,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>17</v>
       </c>
@@ -5392,7 +5398,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>17</v>
       </c>
@@ -5430,7 +5436,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>17</v>
       </c>
@@ -5468,7 +5474,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>17</v>
       </c>
@@ -5506,7 +5512,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>17</v>
       </c>
@@ -5544,7 +5550,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>17</v>
       </c>
@@ -5582,7 +5588,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>17</v>
       </c>
@@ -5620,7 +5626,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>17</v>
       </c>
@@ -5658,7 +5664,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>17</v>
       </c>
@@ -5696,7 +5702,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>17</v>
       </c>
@@ -5734,7 +5740,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>22</v>
       </c>
@@ -5772,7 +5778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>22</v>
       </c>
@@ -5810,7 +5816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>22</v>
       </c>
@@ -5848,7 +5854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>22</v>
       </c>
@@ -5886,7 +5892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>22</v>
       </c>
@@ -5924,7 +5930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>22</v>
       </c>
@@ -5962,7 +5968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>22</v>
       </c>
@@ -6000,7 +6006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>22</v>
       </c>
@@ -6038,7 +6044,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>17</v>
       </c>
@@ -6076,7 +6082,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>32</v>
       </c>
@@ -6114,7 +6120,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>24</v>
       </c>
@@ -6152,7 +6158,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>24</v>
       </c>
@@ -6190,7 +6196,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>17</v>
       </c>
@@ -6228,7 +6234,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>24</v>
       </c>
@@ -6266,7 +6272,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>24</v>
       </c>
@@ -6304,7 +6310,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>22</v>
       </c>
@@ -6342,7 +6348,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>492</v>
       </c>
@@ -6380,7 +6386,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>492</v>
       </c>
@@ -6418,7 +6424,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>32</v>
       </c>
@@ -6456,7 +6462,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>492</v>
       </c>
@@ -6494,7 +6500,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>492</v>
       </c>
@@ -6532,7 +6538,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>492</v>
       </c>
@@ -6570,7 +6576,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>492</v>
       </c>
@@ -6608,7 +6614,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>24</v>
       </c>
@@ -6646,7 +6652,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>24</v>
       </c>
@@ -6684,7 +6690,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>20</v>
       </c>
@@ -6722,7 +6728,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>32</v>
       </c>
@@ -6760,7 +6766,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>32</v>
       </c>
@@ -6798,7 +6804,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>492</v>
       </c>
@@ -6836,7 +6842,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>27</v>
       </c>
@@ -6874,7 +6880,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>32</v>
       </c>
@@ -6912,7 +6918,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>492</v>
       </c>
@@ -6950,7 +6956,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>24</v>
       </c>
@@ -6988,7 +6994,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>24</v>
       </c>
@@ -7026,7 +7032,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>24</v>
       </c>
@@ -7064,7 +7070,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>24</v>
       </c>
@@ -7102,7 +7108,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>27</v>
       </c>
@@ -7140,7 +7146,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>492</v>
       </c>
@@ -7178,7 +7184,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>27</v>
       </c>
@@ -7216,7 +7222,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>20</v>
       </c>
@@ -7254,7 +7260,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>17</v>
       </c>
@@ -7292,7 +7298,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>24</v>
       </c>
@@ -7330,7 +7336,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>24</v>
       </c>
@@ -7368,7 +7374,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>24</v>
       </c>
@@ -7406,7 +7412,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>24</v>
       </c>
@@ -7444,7 +7450,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>27</v>
       </c>
@@ -7482,7 +7488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>24</v>
       </c>
@@ -7520,7 +7526,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>24</v>
       </c>
@@ -7558,7 +7564,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>24</v>
       </c>
@@ -7596,7 +7602,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>24</v>
       </c>
@@ -7634,7 +7640,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>24</v>
       </c>
@@ -7672,7 +7678,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>24</v>
       </c>
@@ -7710,7 +7716,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>27</v>
       </c>
@@ -7748,7 +7754,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>24</v>
       </c>
@@ -7786,7 +7792,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>24</v>
       </c>
@@ -7824,7 +7830,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>32</v>
       </c>
@@ -7862,7 +7868,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>20</v>
       </c>
@@ -7900,7 +7906,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>17</v>
       </c>
@@ -7938,7 +7944,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>27</v>
       </c>
@@ -7976,7 +7982,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>24</v>
       </c>
@@ -8014,7 +8020,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>24</v>
       </c>
@@ -8052,7 +8058,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>24</v>
       </c>
@@ -8090,7 +8096,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>24</v>
       </c>
@@ -8128,7 +8134,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>492</v>
       </c>
@@ -8166,7 +8172,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>27</v>
       </c>
@@ -8204,7 +8210,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>32</v>
       </c>
@@ -8242,7 +8248,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>17</v>
       </c>
@@ -8280,7 +8286,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>27</v>
       </c>
@@ -8318,7 +8324,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>20</v>
       </c>
@@ -8356,7 +8362,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>22</v>
       </c>
@@ -8394,7 +8400,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>20</v>
       </c>
@@ -8432,7 +8438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>27</v>
       </c>
@@ -8470,7 +8476,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>17</v>
       </c>
@@ -8508,7 +8514,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>24</v>
       </c>
@@ -8546,7 +8552,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>24</v>
       </c>
@@ -8584,7 +8590,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>32</v>
       </c>
@@ -8622,7 +8628,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>492</v>
       </c>
@@ -8660,7 +8666,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>492</v>
       </c>
@@ -8698,7 +8704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>492</v>
       </c>
@@ -8736,7 +8742,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>20</v>
       </c>
@@ -8774,7 +8780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>20</v>
       </c>
@@ -8812,7 +8818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>27</v>
       </c>
@@ -8850,7 +8856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>27</v>
       </c>
@@ -8888,7 +8894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>22</v>
       </c>
@@ -8926,7 +8932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>22</v>
       </c>
@@ -8964,7 +8970,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>17</v>
       </c>
@@ -9002,7 +9008,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>17</v>
       </c>
@@ -9040,7 +9046,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>17</v>
       </c>
@@ -9078,7 +9084,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>17</v>
       </c>
@@ -9116,7 +9122,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>17</v>
       </c>
@@ -9154,7 +9160,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>17</v>
       </c>
@@ -9192,7 +9198,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>17</v>
       </c>
@@ -9230,7 +9236,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>17</v>
       </c>
@@ -9268,7 +9274,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>17</v>
       </c>
@@ -9306,7 +9312,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>17</v>
       </c>
@@ -9344,7 +9350,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>20</v>
       </c>
@@ -9382,7 +9388,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>24</v>
       </c>
@@ -9420,7 +9426,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>24</v>
       </c>
@@ -9458,7 +9464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>24</v>
       </c>
@@ -9496,7 +9502,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>24</v>
       </c>
@@ -9534,7 +9540,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>24</v>
       </c>
@@ -9572,7 +9578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>24</v>
       </c>
@@ -9610,7 +9616,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>24</v>
       </c>
@@ -9648,7 +9654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>24</v>
       </c>
@@ -9686,7 +9692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>24</v>
       </c>
@@ -9724,7 +9730,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>24</v>
       </c>
@@ -9762,7 +9768,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>24</v>
       </c>
@@ -9800,7 +9806,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>24</v>
       </c>
@@ -9838,7 +9844,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>24</v>
       </c>
@@ -9876,7 +9882,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>24</v>
       </c>
@@ -9914,7 +9920,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>27</v>
       </c>
@@ -9952,7 +9958,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>27</v>
       </c>
@@ -9990,7 +9996,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>22</v>
       </c>
@@ -10028,7 +10034,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>32</v>
       </c>
@@ -10066,7 +10072,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>27</v>
       </c>
@@ -10104,7 +10110,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>20</v>
       </c>
@@ -10142,7 +10148,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>32</v>
       </c>
@@ -10180,7 +10186,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>492</v>
       </c>
@@ -10218,7 +10224,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>492</v>
       </c>
@@ -10256,7 +10262,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>492</v>
       </c>
@@ -10294,7 +10300,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>492</v>
       </c>
@@ -10332,7 +10338,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>492</v>
       </c>
@@ -10370,7 +10376,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>492</v>
       </c>
@@ -10408,7 +10414,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>492</v>
       </c>
@@ -10446,7 +10452,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>24</v>
       </c>
@@ -10484,7 +10490,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>24</v>
       </c>
@@ -10522,7 +10528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>24</v>
       </c>
@@ -10560,7 +10566,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>24</v>
       </c>
@@ -10598,7 +10604,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>24</v>
       </c>
@@ -10636,7 +10642,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>24</v>
       </c>
@@ -10674,7 +10680,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>27</v>
       </c>
@@ -10712,7 +10718,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>27</v>
       </c>
@@ -10750,7 +10756,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>492</v>
       </c>
@@ -10788,7 +10794,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>27</v>
       </c>
@@ -10826,7 +10832,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>20</v>
       </c>
@@ -10864,7 +10870,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>27</v>
       </c>
@@ -10902,7 +10908,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>22</v>
       </c>
@@ -10940,7 +10946,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>17</v>
       </c>
@@ -10978,7 +10984,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>20</v>
       </c>
@@ -11016,7 +11022,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>17</v>
       </c>
@@ -11054,7 +11060,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>20</v>
       </c>
@@ -11092,7 +11098,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>32</v>
       </c>
@@ -11130,7 +11136,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>27</v>
       </c>
@@ -11168,7 +11174,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>27</v>
       </c>
@@ -11206,7 +11212,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>22</v>
       </c>
@@ -11244,7 +11250,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>22</v>
       </c>
@@ -11282,7 +11288,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>22</v>
       </c>
@@ -11320,7 +11326,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>17</v>
       </c>
@@ -11358,7 +11364,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>492</v>
       </c>
@@ -11396,7 +11402,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>20</v>
       </c>
@@ -11434,7 +11440,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>32</v>
       </c>
@@ -11472,7 +11478,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>17</v>
       </c>
@@ -11510,7 +11516,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>27</v>
       </c>
@@ -11548,7 +11554,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>22</v>
       </c>
@@ -11586,7 +11592,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>20</v>
       </c>
@@ -11624,7 +11630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>20</v>
       </c>
@@ -11662,7 +11668,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>492</v>
       </c>
@@ -11700,7 +11706,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>24</v>
       </c>
@@ -11738,7 +11744,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>24</v>
       </c>
@@ -11776,7 +11782,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>20</v>
       </c>
@@ -11814,7 +11820,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>27</v>
       </c>
@@ -11852,7 +11858,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>22</v>
       </c>
@@ -11890,7 +11896,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>22</v>
       </c>
@@ -11928,7 +11934,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>27</v>
       </c>
@@ -11966,7 +11972,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>27</v>
       </c>
@@ -12004,7 +12010,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>27</v>
       </c>
@@ -12042,7 +12048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>20</v>
       </c>
@@ -12080,7 +12086,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>22</v>
       </c>
@@ -12118,7 +12124,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>27</v>
       </c>
@@ -12156,7 +12162,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>17</v>
       </c>
@@ -12194,7 +12200,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>492</v>
       </c>
@@ -12232,7 +12238,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>32</v>
       </c>
@@ -12270,7 +12276,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>24</v>
       </c>
@@ -12308,7 +12314,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>24</v>
       </c>
@@ -12346,7 +12352,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>27</v>
       </c>
@@ -12384,7 +12390,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>27</v>
       </c>
@@ -12422,7 +12428,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>22</v>
       </c>
@@ -12460,7 +12466,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>24</v>
       </c>
@@ -12498,7 +12504,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>24</v>
       </c>
@@ -12536,7 +12542,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>24</v>
       </c>
@@ -12574,7 +12580,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>24</v>
       </c>
@@ -12612,7 +12618,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>24</v>
       </c>
@@ -12650,7 +12656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>24</v>
       </c>
@@ -12688,7 +12694,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>24</v>
       </c>
@@ -12726,7 +12732,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>24</v>
       </c>
@@ -12764,7 +12770,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>24</v>
       </c>
@@ -12802,7 +12808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>24</v>
       </c>
@@ -12840,7 +12846,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>24</v>
       </c>
@@ -12878,7 +12884,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>24</v>
       </c>
@@ -12916,7 +12922,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>24</v>
       </c>
@@ -12954,7 +12960,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>24</v>
       </c>
@@ -12992,7 +12998,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>24</v>
       </c>
@@ -13030,7 +13036,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>492</v>
       </c>
@@ -13068,7 +13074,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>24</v>
       </c>
@@ -13106,7 +13112,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>24</v>
       </c>
@@ -13144,7 +13150,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>24</v>
       </c>
@@ -13182,7 +13188,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>24</v>
       </c>
@@ -13220,7 +13226,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>20</v>
       </c>
@@ -13258,7 +13264,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>22</v>
       </c>
@@ -13296,7 +13302,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>492</v>
       </c>
@@ -13334,7 +13340,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>17</v>
       </c>
@@ -13372,7 +13378,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>20</v>
       </c>
@@ -13410,7 +13416,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>27</v>
       </c>
@@ -13448,7 +13454,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>27</v>
       </c>
@@ -13486,7 +13492,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>27</v>
       </c>
@@ -13524,7 +13530,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>20</v>
       </c>
@@ -13562,7 +13568,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>20</v>
       </c>
@@ -13600,7 +13606,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>32</v>
       </c>
@@ -13638,7 +13644,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>22</v>
       </c>
@@ -13676,7 +13682,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>17</v>
       </c>
@@ -13714,7 +13720,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>27</v>
       </c>
@@ -13752,7 +13758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>24</v>
       </c>
@@ -13790,7 +13796,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>24</v>
       </c>
@@ -13828,7 +13834,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>492</v>
       </c>
@@ -13866,7 +13872,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>492</v>
       </c>
@@ -13904,7 +13910,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>20</v>
       </c>
@@ -13942,7 +13948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>20</v>
       </c>
@@ -13980,7 +13986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>20</v>
       </c>
@@ -14018,7 +14024,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>27</v>
       </c>
@@ -14056,7 +14062,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>27</v>
       </c>
@@ -14094,7 +14100,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>27</v>
       </c>
@@ -14132,7 +14138,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>24</v>
       </c>
@@ -14170,7 +14176,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>24</v>
       </c>
@@ -14208,7 +14214,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>17</v>
       </c>
@@ -14246,7 +14252,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>17</v>
       </c>
@@ -14284,7 +14290,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>24</v>
       </c>
@@ -14322,7 +14328,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>24</v>
       </c>
@@ -14360,7 +14366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>492</v>
       </c>
@@ -14398,7 +14404,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>492</v>
       </c>
@@ -14436,7 +14442,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>20</v>
       </c>
@@ -14474,7 +14480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>20</v>
       </c>
@@ -14512,7 +14518,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="334" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>20</v>
       </c>
@@ -14550,7 +14556,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="335" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>27</v>
       </c>
@@ -14588,7 +14594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>27</v>
       </c>
@@ -14626,7 +14632,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="337" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>27</v>
       </c>
@@ -14664,7 +14670,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="338" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>24</v>
       </c>
@@ -14702,7 +14708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>24</v>
       </c>
@@ -14740,7 +14746,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="340" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>24</v>
       </c>
@@ -14778,7 +14784,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="341" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>17</v>
       </c>
@@ -14816,7 +14822,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="342" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>17</v>
       </c>
@@ -14854,7 +14860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="343" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>17</v>
       </c>
@@ -14892,7 +14898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>17</v>
       </c>
@@ -14930,7 +14936,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="345" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>492</v>
       </c>
@@ -14968,7 +14974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>24</v>
       </c>
@@ -15006,7 +15012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>492</v>
       </c>
@@ -15044,7 +15050,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="348" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>17</v>
       </c>
@@ -15082,7 +15088,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="349" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>492</v>
       </c>
@@ -15120,7 +15126,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="350" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>32</v>
       </c>
@@ -15158,7 +15164,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="351" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>24</v>
       </c>
@@ -15196,7 +15202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="352" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>24</v>
       </c>
@@ -15234,7 +15240,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="353" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>24</v>
       </c>
@@ -15272,7 +15278,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="354" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>492</v>
       </c>
@@ -15310,7 +15316,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="355" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>24</v>
       </c>
@@ -15348,7 +15354,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="356" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>24</v>
       </c>
@@ -15386,7 +15392,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="357" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>24</v>
       </c>
@@ -15424,7 +15430,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="358" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>24</v>
       </c>
@@ -15462,7 +15468,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="359" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>24</v>
       </c>
@@ -15500,7 +15506,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="360" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>24</v>
       </c>
@@ -15538,7 +15544,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="361" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>24</v>
       </c>
@@ -15576,7 +15582,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="362" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>24</v>
       </c>
@@ -15614,7 +15620,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="363" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>24</v>
       </c>
@@ -15652,7 +15658,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="364" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>24</v>
       </c>
@@ -15690,7 +15696,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="365" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>492</v>
       </c>
@@ -15728,7 +15734,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="366" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>17</v>
       </c>
@@ -15766,7 +15772,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="367" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>24</v>
       </c>
@@ -15804,7 +15810,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="368" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>24</v>
       </c>
@@ -15842,7 +15848,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>17</v>
       </c>
@@ -15880,7 +15886,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="370" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>492</v>
       </c>
@@ -15918,7 +15924,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
         <v>27</v>
       </c>
@@ -15956,7 +15962,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="372" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>22</v>
       </c>
@@ -15994,7 +16000,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="373" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>27</v>
       </c>
@@ -16032,7 +16038,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="374" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>32</v>
       </c>
@@ -16070,7 +16076,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="375" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
         <v>22</v>
       </c>
@@ -16108,7 +16114,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="376" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>24</v>
       </c>
@@ -16146,7 +16152,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="377" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>24</v>
       </c>
@@ -16184,7 +16190,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="378" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>492</v>
       </c>
@@ -16222,7 +16228,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="379" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>24</v>
       </c>
@@ -16260,7 +16266,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="380" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>24</v>
       </c>
@@ -16298,7 +16304,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="381" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>492</v>
       </c>
@@ -16336,7 +16342,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="382" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>27</v>
       </c>
@@ -16374,7 +16380,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="383" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>27</v>
       </c>
@@ -16412,7 +16418,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="384" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>27</v>
       </c>
@@ -16450,7 +16456,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="385" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="385" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
         <v>27</v>
       </c>
@@ -16488,7 +16494,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="386" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>27</v>
       </c>
@@ -16526,7 +16532,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="387" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="387" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
         <v>27</v>
       </c>
@@ -16564,7 +16570,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="388" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
         <v>27</v>
       </c>
@@ -16602,7 +16608,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="389" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="389" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
         <v>27</v>
       </c>
@@ -16640,7 +16646,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="390" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="390" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>27</v>
       </c>
@@ -16678,7 +16684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="391" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>27</v>
       </c>
@@ -16716,7 +16722,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="392" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
         <v>27</v>
       </c>
@@ -16754,7 +16760,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="393" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>27</v>
       </c>
@@ -16792,7 +16798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="394" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>27</v>
       </c>
@@ -16830,7 +16836,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="395" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>27</v>
       </c>
@@ -16868,7 +16874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="396" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
         <v>492</v>
       </c>
@@ -16906,7 +16912,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="397" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
         <v>492</v>
       </c>
@@ -16944,7 +16950,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="398" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
         <v>492</v>
       </c>
@@ -16982,7 +16988,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="399" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
         <v>492</v>
       </c>
@@ -17020,7 +17026,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="400" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>492</v>
       </c>
@@ -17058,7 +17064,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="401" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="401" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>492</v>
       </c>
@@ -17096,7 +17102,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="402" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>492</v>
       </c>
@@ -17134,7 +17140,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="403" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>492</v>
       </c>
@@ -17172,7 +17178,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="404" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
         <v>492</v>
       </c>
@@ -17210,7 +17216,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="405" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
         <v>492</v>
       </c>
@@ -17248,7 +17254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="406" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>20</v>
       </c>
@@ -17286,7 +17292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="407" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
         <v>20</v>
       </c>
@@ -17324,7 +17330,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="408" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
         <v>20</v>
       </c>
@@ -17362,7 +17368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="409" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
         <v>27</v>
       </c>
@@ -17400,7 +17406,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="410" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>27</v>
       </c>
@@ -17438,7 +17444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="411" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
         <v>24</v>
       </c>
@@ -17476,7 +17482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="412" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
         <v>24</v>
       </c>
@@ -17514,7 +17520,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="413" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="413" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
         <v>24</v>
       </c>
@@ -17552,7 +17558,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="414" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="414" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>17</v>
       </c>
@@ -17590,7 +17596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="415" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
         <v>17</v>
       </c>
@@ -17628,7 +17634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="416" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="416" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
         <v>24</v>
       </c>
@@ -17666,7 +17672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="417" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
         <v>492</v>
       </c>
@@ -17704,7 +17710,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="418" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="418" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
         <v>492</v>
       </c>
@@ -17742,7 +17748,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="419" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
         <v>492</v>
       </c>
@@ -17780,7 +17786,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="420" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
         <v>17</v>
       </c>
@@ -17818,7 +17824,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="421" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="421" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
         <v>20</v>
       </c>
@@ -17856,7 +17862,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="422" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
         <v>27</v>
       </c>
@@ -17894,7 +17900,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="423" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
         <v>20</v>
       </c>
@@ -17932,7 +17938,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="424" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
         <v>27</v>
       </c>
@@ -17970,7 +17976,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="425" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
         <v>32</v>
       </c>
@@ -18008,7 +18014,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="426" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
         <v>22</v>
       </c>
@@ -18046,7 +18052,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="427" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="427" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
         <v>20</v>
       </c>
@@ -18084,7 +18090,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="428" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
         <v>20</v>
       </c>
@@ -18122,7 +18128,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="429" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="429" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
         <v>17</v>
       </c>
@@ -18160,7 +18166,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="430" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
         <v>27</v>
       </c>
@@ -18198,7 +18204,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="431" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="431" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
         <v>32</v>
       </c>
@@ -18236,7 +18242,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="432" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
         <v>27</v>
       </c>
@@ -18274,7 +18280,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="433" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
         <v>17</v>
       </c>
@@ -18312,7 +18318,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="434" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
         <v>17</v>
       </c>
@@ -18350,7 +18356,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="435" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
         <v>27</v>
       </c>
@@ -18388,7 +18394,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="436" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="436" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
         <v>20</v>
       </c>
@@ -18426,7 +18432,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="437" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="437" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
         <v>17</v>
       </c>
@@ -18464,7 +18470,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="438" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="438" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
         <v>492</v>
       </c>
@@ -18502,7 +18508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="439" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="439" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
         <v>20</v>
       </c>
@@ -18540,7 +18546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="440" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="440" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
         <v>27</v>
       </c>
@@ -18578,7 +18584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="441" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="441" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
         <v>32</v>
       </c>
@@ -18616,7 +18622,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="442" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="442" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
         <v>17</v>
       </c>
@@ -18654,7 +18660,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="443" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="443" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
         <v>27</v>
       </c>
@@ -18692,7 +18698,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="444" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="444" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
         <v>32</v>
       </c>
@@ -18730,7 +18736,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="445" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="445" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
         <v>492</v>
       </c>
@@ -18768,7 +18774,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="446" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="446" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
         <v>20</v>
       </c>
@@ -18806,7 +18812,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="447" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="447" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
         <v>20</v>
       </c>
@@ -18844,7 +18850,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="448" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="448" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
         <v>492</v>
       </c>
@@ -18882,7 +18888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="449" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
         <v>492</v>
       </c>
@@ -18920,7 +18926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="450" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
         <v>492</v>
       </c>
@@ -18958,7 +18964,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="451" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
         <v>20</v>
       </c>
@@ -18996,7 +19002,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="452" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
         <v>32</v>
       </c>
@@ -19034,7 +19040,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="453" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="453" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
         <v>27</v>
       </c>
@@ -19072,7 +19078,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="454" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
         <v>22</v>
       </c>
@@ -19110,7 +19116,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="455" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="455" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
         <v>24</v>
       </c>
@@ -19148,7 +19154,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="456" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
         <v>17</v>
       </c>
@@ -19186,7 +19192,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="457" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="457" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
         <v>24</v>
       </c>
@@ -19224,7 +19230,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="458" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="458" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
         <v>22</v>
       </c>
@@ -19262,7 +19268,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="459" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="459" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
         <v>17</v>
       </c>
@@ -19300,7 +19306,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="460" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="460" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
         <v>24</v>
       </c>
@@ -19338,7 +19344,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="461" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="461" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
         <v>24</v>
       </c>
@@ -19376,7 +19382,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="462" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="462" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
         <v>20</v>
       </c>
@@ -19414,7 +19420,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="463" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="463" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
         <v>32</v>
       </c>
@@ -19452,7 +19458,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="464" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="464" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
         <v>17</v>
       </c>
@@ -19490,7 +19496,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="465" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="465" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
         <v>27</v>
       </c>
@@ -19528,7 +19534,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="466" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="466" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
         <v>20</v>
       </c>
@@ -19566,7 +19572,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="467" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="467" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
         <v>20</v>
       </c>
@@ -19604,7 +19610,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="468" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="468" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
         <v>20</v>
       </c>
@@ -19642,7 +19648,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="469" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="469" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
         <v>22</v>
       </c>
@@ -19680,7 +19686,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="470" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="470" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
         <v>20</v>
       </c>
@@ -19718,7 +19724,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="471" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="471" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
         <v>20</v>
       </c>
@@ -19756,7 +19762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="472" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="472" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
         <v>22</v>
       </c>
@@ -19794,7 +19800,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="473" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
         <v>20</v>
       </c>

--- a/data/BerkData.xlsx
+++ b/data/BerkData.xlsx
@@ -1,24 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD24A85-5295-4702-B5EB-B6C1668D4A66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{053DBBFD-397F-4D75-AA98-765A8F0A8F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="5940" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1562,9 +1573,19 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E850A034-3729-4F84-81A0-F1DDCFD4FBCC}" name="Table1" displayName="Table1" ref="A1:L473" totalsRowShown="0">
   <autoFilter ref="A1:L473" xr:uid="{E850A034-3729-4F84-81A0-F1DDCFD4FBCC}">
-    <filterColumn colId="0">
+    <filterColumn colId="1">
       <filters>
-        <filter val="İnşaat Mühendisliği"/>
+        <filter val="MAT 152"/>
+        <filter val="MAT 162"/>
+        <filter val="MAT 222"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="4">
+      <filters>
+        <filter val="2"/>
+        <filter val="3"/>
+        <filter val="4"/>
+        <filter val="5"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -2016,7 +2037,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -2510,7 +2531,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -3080,7 +3101,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>20</v>
       </c>
@@ -3118,7 +3139,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>20</v>
       </c>
@@ -3498,7 +3519,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>20</v>
       </c>
@@ -3536,7 +3557,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>20</v>
       </c>
@@ -3574,7 +3595,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>20</v>
       </c>
@@ -3612,7 +3633,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>20</v>
       </c>
@@ -3954,7 +3975,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>20</v>
       </c>
@@ -4144,7 +4165,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>20</v>
       </c>
@@ -6690,7 +6711,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>20</v>
       </c>
@@ -7222,7 +7243,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>20</v>
       </c>
@@ -7868,7 +7889,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>20</v>
       </c>
@@ -8324,7 +8345,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>20</v>
       </c>
@@ -8400,7 +8421,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>20</v>
       </c>
@@ -8742,7 +8763,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>20</v>
       </c>
@@ -8780,7 +8801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>20</v>
       </c>
@@ -9350,7 +9371,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>20</v>
       </c>
@@ -10110,7 +10131,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>20</v>
       </c>
@@ -10832,7 +10853,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>20</v>
       </c>
@@ -10984,7 +11005,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>20</v>
       </c>
@@ -11060,7 +11081,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>20</v>
       </c>
@@ -11402,7 +11423,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>20</v>
       </c>
@@ -11592,7 +11613,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>20</v>
       </c>
@@ -11630,7 +11651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>20</v>
       </c>
@@ -11668,7 +11689,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="259" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>492</v>
       </c>
@@ -11782,7 +11803,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>20</v>
       </c>
@@ -12086,7 +12107,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="270" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>22</v>
       </c>
@@ -12124,7 +12145,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="271" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>27</v>
       </c>
@@ -12162,7 +12183,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="272" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>17</v>
       </c>
@@ -12200,7 +12221,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="273" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>492</v>
       </c>
@@ -12238,7 +12259,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="274" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>32</v>
       </c>
@@ -12276,7 +12297,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="275" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>24</v>
       </c>
@@ -12314,7 +12335,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="276" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>24</v>
       </c>
@@ -13226,7 +13247,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>20</v>
       </c>
@@ -13378,7 +13399,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>20</v>
       </c>
@@ -13530,7 +13551,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>20</v>
       </c>
@@ -13568,7 +13589,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>20</v>
       </c>
@@ -13910,7 +13931,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>20</v>
       </c>
@@ -13948,7 +13969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>20</v>
       </c>
@@ -13986,7 +14007,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>20</v>
       </c>
@@ -14442,7 +14463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>20</v>
       </c>
@@ -14480,7 +14501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>20</v>
       </c>
@@ -14518,7 +14539,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="334" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>20</v>
       </c>
@@ -17254,7 +17275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="406" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>20</v>
       </c>
@@ -17292,7 +17313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="407" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
         <v>20</v>
       </c>
@@ -17330,7 +17351,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="408" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
         <v>20</v>
       </c>
@@ -17824,7 +17845,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="421" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
         <v>20</v>
       </c>
@@ -17900,7 +17921,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="423" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
         <v>20</v>
       </c>
@@ -18052,7 +18073,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="427" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
         <v>20</v>
       </c>
@@ -18090,7 +18111,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="428" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
         <v>20</v>
       </c>
@@ -18394,7 +18415,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="436" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
         <v>20</v>
       </c>
@@ -18508,7 +18529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="439" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
         <v>20</v>
       </c>
@@ -18774,7 +18795,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="446" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
         <v>20</v>
       </c>
@@ -18812,7 +18833,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="447" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
         <v>20</v>
       </c>
@@ -18964,7 +18985,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="451" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
         <v>20</v>
       </c>
@@ -19382,7 +19403,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="462" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
         <v>20</v>
       </c>
@@ -19534,7 +19555,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="466" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
         <v>20</v>
       </c>
@@ -19572,7 +19593,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="467" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
         <v>20</v>
       </c>
@@ -19610,7 +19631,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="468" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
         <v>20</v>
       </c>
@@ -19686,7 +19707,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="470" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
         <v>20</v>
       </c>
@@ -19724,7 +19745,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="471" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
         <v>20</v>
       </c>
@@ -19800,7 +19821,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="473" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
         <v>20</v>
       </c>

--- a/data/BerkData.xlsx
+++ b/data/BerkData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{053DBBFD-397F-4D75-AA98-765A8F0A8F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53064AC1-F244-4B4B-8775-CBB65AE9FD07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="5940" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -1572,23 +1572,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E850A034-3729-4F84-81A0-F1DDCFD4FBCC}" name="Table1" displayName="Table1" ref="A1:L473" totalsRowShown="0">
-  <autoFilter ref="A1:L473" xr:uid="{E850A034-3729-4F84-81A0-F1DDCFD4FBCC}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="MAT 152"/>
-        <filter val="MAT 162"/>
-        <filter val="MAT 222"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="4">
-      <filters>
-        <filter val="2"/>
-        <filter val="3"/>
-        <filter val="4"/>
-        <filter val="5"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:L473" xr:uid="{E850A034-3729-4F84-81A0-F1DDCFD4FBCC}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{769BB3A9-BC2D-4B0E-97B5-9CDAEEA9BFD5}" name="DepartmentName"/>
     <tableColumn id="2" xr3:uid="{C86EDC24-CDF3-487D-BE22-4DFF16AF6CEC}" name="CourseCode"/>
@@ -1923,7 +1907,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>492</v>
       </c>
@@ -1961,7 +1945,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>492</v>
       </c>
@@ -1999,7 +1983,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>492</v>
       </c>
@@ -2037,7 +2021,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -2075,7 +2059,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -2113,7 +2097,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -2151,7 +2135,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -2189,7 +2173,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -2227,7 +2211,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -2265,7 +2249,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -2303,7 +2287,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -2341,7 +2325,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -2379,7 +2363,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -2417,7 +2401,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -2455,7 +2439,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>492</v>
       </c>
@@ -2493,7 +2477,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>492</v>
       </c>
@@ -2531,7 +2515,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -2569,7 +2553,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -2607,7 +2591,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -2645,7 +2629,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -2683,7 +2667,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -2721,7 +2705,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>17</v>
       </c>
@@ -2759,7 +2743,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -2797,7 +2781,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -2835,7 +2819,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>32</v>
       </c>
@@ -2873,7 +2857,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>24</v>
       </c>
@@ -2911,7 +2895,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>24</v>
       </c>
@@ -2949,7 +2933,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>24</v>
       </c>
@@ -2987,7 +2971,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>24</v>
       </c>
@@ -3025,7 +3009,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -3063,7 +3047,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>24</v>
       </c>
@@ -3101,7 +3085,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>20</v>
       </c>
@@ -3139,7 +3123,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>20</v>
       </c>
@@ -3177,7 +3161,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>32</v>
       </c>
@@ -3215,7 +3199,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>27</v>
       </c>
@@ -3253,7 +3237,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>24</v>
       </c>
@@ -3291,7 +3275,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>24</v>
       </c>
@@ -3329,7 +3313,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>24</v>
       </c>
@@ -3367,7 +3351,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>24</v>
       </c>
@@ -3405,7 +3389,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>27</v>
       </c>
@@ -3443,7 +3427,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>27</v>
       </c>
@@ -3481,7 +3465,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>27</v>
       </c>
@@ -3519,7 +3503,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>20</v>
       </c>
@@ -3557,7 +3541,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>20</v>
       </c>
@@ -3595,7 +3579,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>20</v>
       </c>
@@ -3633,7 +3617,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>20</v>
       </c>
@@ -3671,7 +3655,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>27</v>
       </c>
@@ -3709,7 +3693,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>22</v>
       </c>
@@ -3747,7 +3731,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>17</v>
       </c>
@@ -3785,7 +3769,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>17</v>
       </c>
@@ -3823,7 +3807,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>24</v>
       </c>
@@ -3861,7 +3845,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>24</v>
       </c>
@@ -3899,7 +3883,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>22</v>
       </c>
@@ -3937,7 +3921,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>32</v>
       </c>
@@ -3975,7 +3959,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>20</v>
       </c>
@@ -4013,7 +3997,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>32</v>
       </c>
@@ -4051,7 +4035,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>24</v>
       </c>
@@ -4089,7 +4073,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -4127,7 +4111,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>24</v>
       </c>
@@ -4165,7 +4149,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>20</v>
       </c>
@@ -4203,7 +4187,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>32</v>
       </c>
@@ -4241,7 +4225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>32</v>
       </c>
@@ -4279,7 +4263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>32</v>
       </c>
@@ -4317,7 +4301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>32</v>
       </c>
@@ -4355,7 +4339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>32</v>
       </c>
@@ -4393,7 +4377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>32</v>
       </c>
@@ -4431,7 +4415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>32</v>
       </c>
@@ -4469,7 +4453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>32</v>
       </c>
@@ -4507,7 +4491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>32</v>
       </c>
@@ -4545,7 +4529,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>32</v>
       </c>
@@ -4583,7 +4567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>32</v>
       </c>
@@ -4621,7 +4605,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>32</v>
       </c>
@@ -4659,7 +4643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>27</v>
       </c>
@@ -4697,7 +4681,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>27</v>
       </c>
@@ -4735,7 +4719,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>27</v>
       </c>
@@ -4773,7 +4757,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>27</v>
       </c>
@@ -4811,7 +4795,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>27</v>
       </c>
@@ -4849,7 +4833,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>27</v>
       </c>
@@ -4887,7 +4871,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>27</v>
       </c>
@@ -4925,7 +4909,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>27</v>
       </c>
@@ -4963,7 +4947,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>27</v>
       </c>
@@ -5001,7 +4985,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>27</v>
       </c>
@@ -5039,7 +5023,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>27</v>
       </c>
@@ -5077,7 +5061,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>27</v>
       </c>
@@ -5115,7 +5099,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>27</v>
       </c>
@@ -5153,7 +5137,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>27</v>
       </c>
@@ -5191,7 +5175,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>17</v>
       </c>
@@ -5229,7 +5213,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>17</v>
       </c>
@@ -5267,7 +5251,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>17</v>
       </c>
@@ -5305,7 +5289,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>17</v>
       </c>
@@ -5343,7 +5327,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>17</v>
       </c>
@@ -5381,7 +5365,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>17</v>
       </c>
@@ -5419,7 +5403,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>17</v>
       </c>
@@ -5457,7 +5441,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>17</v>
       </c>
@@ -5495,7 +5479,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>17</v>
       </c>
@@ -5533,7 +5517,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>17</v>
       </c>
@@ -5571,7 +5555,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>17</v>
       </c>
@@ -5609,7 +5593,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>17</v>
       </c>
@@ -5647,7 +5631,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>17</v>
       </c>
@@ -5685,7 +5669,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>17</v>
       </c>
@@ -5723,7 +5707,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>17</v>
       </c>
@@ -5761,7 +5745,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>22</v>
       </c>
@@ -5799,7 +5783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>22</v>
       </c>
@@ -5837,7 +5821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>22</v>
       </c>
@@ -5875,7 +5859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>22</v>
       </c>
@@ -5913,7 +5897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>22</v>
       </c>
@@ -5951,7 +5935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>22</v>
       </c>
@@ -5989,7 +5973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>22</v>
       </c>
@@ -6027,7 +6011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>22</v>
       </c>
@@ -6065,7 +6049,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>17</v>
       </c>
@@ -6103,7 +6087,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>32</v>
       </c>
@@ -6141,7 +6125,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>24</v>
       </c>
@@ -6179,7 +6163,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>24</v>
       </c>
@@ -6217,7 +6201,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>17</v>
       </c>
@@ -6255,7 +6239,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>24</v>
       </c>
@@ -6293,7 +6277,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>24</v>
       </c>
@@ -6331,7 +6315,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>22</v>
       </c>
@@ -6369,7 +6353,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>492</v>
       </c>
@@ -6407,7 +6391,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>492</v>
       </c>
@@ -6445,7 +6429,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>32</v>
       </c>
@@ -6483,7 +6467,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>492</v>
       </c>
@@ -6521,7 +6505,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>492</v>
       </c>
@@ -6559,7 +6543,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="124" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>492</v>
       </c>
@@ -6597,7 +6581,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="125" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>492</v>
       </c>
@@ -6635,7 +6619,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>24</v>
       </c>
@@ -6673,7 +6657,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="127" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>24</v>
       </c>
@@ -6711,7 +6695,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>20</v>
       </c>
@@ -6749,7 +6733,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="129" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>32</v>
       </c>
@@ -6787,7 +6771,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="130" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>32</v>
       </c>
@@ -6825,7 +6809,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="131" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>492</v>
       </c>
@@ -6863,7 +6847,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="132" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>27</v>
       </c>
@@ -6901,7 +6885,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="133" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>32</v>
       </c>
@@ -6939,7 +6923,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="134" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>492</v>
       </c>
@@ -6977,7 +6961,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="135" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>24</v>
       </c>
@@ -7015,7 +6999,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="136" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>24</v>
       </c>
@@ -7053,7 +7037,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="137" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>24</v>
       </c>
@@ -7091,7 +7075,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="138" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>24</v>
       </c>
@@ -7129,7 +7113,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="139" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>27</v>
       </c>
@@ -7167,7 +7151,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="140" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>492</v>
       </c>
@@ -7205,7 +7189,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="141" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>27</v>
       </c>
@@ -7243,7 +7227,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="142" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>20</v>
       </c>
@@ -7281,7 +7265,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="143" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>17</v>
       </c>
@@ -7319,7 +7303,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="144" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>24</v>
       </c>
@@ -7357,7 +7341,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="145" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>24</v>
       </c>
@@ -7395,7 +7379,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="146" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>24</v>
       </c>
@@ -7433,7 +7417,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="147" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>24</v>
       </c>
@@ -7471,7 +7455,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="148" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>27</v>
       </c>
@@ -7509,7 +7493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>24</v>
       </c>
@@ -7547,7 +7531,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="150" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>24</v>
       </c>
@@ -7585,7 +7569,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="151" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>24</v>
       </c>
@@ -7623,7 +7607,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="152" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>24</v>
       </c>
@@ -7661,7 +7645,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="153" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>24</v>
       </c>
@@ -7699,7 +7683,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="154" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>24</v>
       </c>
@@ -7737,7 +7721,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="155" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>27</v>
       </c>
@@ -7775,7 +7759,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="156" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>24</v>
       </c>
@@ -7813,7 +7797,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="157" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>24</v>
       </c>
@@ -7851,7 +7835,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="158" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>32</v>
       </c>
@@ -7889,7 +7873,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="159" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>20</v>
       </c>
@@ -7927,7 +7911,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="160" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>17</v>
       </c>
@@ -7965,7 +7949,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="161" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>27</v>
       </c>
@@ -8003,7 +7987,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="162" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>24</v>
       </c>
@@ -8041,7 +8025,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="163" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>24</v>
       </c>
@@ -8079,7 +8063,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="164" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>24</v>
       </c>
@@ -8117,7 +8101,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="165" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>24</v>
       </c>
@@ -8155,7 +8139,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="166" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>492</v>
       </c>
@@ -8193,7 +8177,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="167" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>27</v>
       </c>
@@ -8231,7 +8215,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="168" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>32</v>
       </c>
@@ -8269,7 +8253,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>17</v>
       </c>
@@ -8307,7 +8291,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="170" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>27</v>
       </c>
@@ -8345,7 +8329,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="171" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>20</v>
       </c>
@@ -8383,7 +8367,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="172" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>22</v>
       </c>
@@ -8421,7 +8405,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="173" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>20</v>
       </c>
@@ -8459,7 +8443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>27</v>
       </c>
@@ -8497,7 +8481,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="175" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>17</v>
       </c>
@@ -8535,7 +8519,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="176" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>24</v>
       </c>
@@ -8573,7 +8557,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="177" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>24</v>
       </c>
@@ -8611,7 +8595,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="178" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>32</v>
       </c>
@@ -8649,7 +8633,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="179" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>492</v>
       </c>
@@ -8687,7 +8671,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>492</v>
       </c>
@@ -8725,7 +8709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>492</v>
       </c>
@@ -8763,7 +8747,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="182" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>20</v>
       </c>
@@ -8801,7 +8785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>20</v>
       </c>
@@ -8839,7 +8823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>27</v>
       </c>
@@ -8877,7 +8861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>27</v>
       </c>
@@ -8915,7 +8899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>22</v>
       </c>
@@ -8953,7 +8937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>22</v>
       </c>
@@ -8991,7 +8975,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="188" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>17</v>
       </c>
@@ -9029,7 +9013,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="189" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>17</v>
       </c>
@@ -9067,7 +9051,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="190" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>17</v>
       </c>
@@ -9105,7 +9089,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="191" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>17</v>
       </c>
@@ -9143,7 +9127,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="192" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>17</v>
       </c>
@@ -9181,7 +9165,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="193" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>17</v>
       </c>
@@ -9219,7 +9203,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="194" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>17</v>
       </c>
@@ -9257,7 +9241,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="195" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>17</v>
       </c>
@@ -9295,7 +9279,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="196" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>17</v>
       </c>
@@ -9333,7 +9317,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="197" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>17</v>
       </c>
@@ -9371,7 +9355,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="198" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>20</v>
       </c>
@@ -9409,7 +9393,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="199" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>24</v>
       </c>
@@ -9447,7 +9431,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="200" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>24</v>
       </c>
@@ -9485,7 +9469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>24</v>
       </c>
@@ -9523,7 +9507,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="202" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>24</v>
       </c>
@@ -9561,7 +9545,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="203" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>24</v>
       </c>
@@ -9599,7 +9583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>24</v>
       </c>
@@ -9637,7 +9621,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="205" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>24</v>
       </c>
@@ -9675,7 +9659,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>24</v>
       </c>
@@ -9713,7 +9697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>24</v>
       </c>
@@ -9751,7 +9735,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="208" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>24</v>
       </c>
@@ -9789,7 +9773,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="209" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>24</v>
       </c>
@@ -9827,7 +9811,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="210" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>24</v>
       </c>
@@ -9865,7 +9849,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="211" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>24</v>
       </c>
@@ -9903,7 +9887,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="212" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>24</v>
       </c>
@@ -9941,7 +9925,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="213" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>27</v>
       </c>
@@ -9979,7 +9963,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="214" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>27</v>
       </c>
@@ -10017,7 +10001,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="215" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>22</v>
       </c>
@@ -10055,7 +10039,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="216" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>32</v>
       </c>
@@ -10093,7 +10077,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="217" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>27</v>
       </c>
@@ -10131,7 +10115,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="218" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>20</v>
       </c>
@@ -10169,7 +10153,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="219" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>32</v>
       </c>
@@ -10207,7 +10191,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="220" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>492</v>
       </c>
@@ -10245,7 +10229,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="221" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>492</v>
       </c>
@@ -10283,7 +10267,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="222" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>492</v>
       </c>
@@ -10321,7 +10305,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="223" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>492</v>
       </c>
@@ -10359,7 +10343,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="224" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>492</v>
       </c>
@@ -10397,7 +10381,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="225" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>492</v>
       </c>
@@ -10435,7 +10419,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="226" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>492</v>
       </c>
@@ -10473,7 +10457,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="227" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>24</v>
       </c>
@@ -10511,7 +10495,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="228" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>24</v>
       </c>
@@ -10549,7 +10533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>24</v>
       </c>
@@ -10587,7 +10571,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="230" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>24</v>
       </c>
@@ -10625,7 +10609,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="231" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>24</v>
       </c>
@@ -10663,7 +10647,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="232" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>24</v>
       </c>
@@ -10701,7 +10685,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="233" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>27</v>
       </c>
@@ -10739,7 +10723,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="234" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>27</v>
       </c>
@@ -10777,7 +10761,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="235" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>492</v>
       </c>
@@ -10815,7 +10799,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="236" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>27</v>
       </c>
@@ -10853,7 +10837,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="237" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>20</v>
       </c>
@@ -10891,7 +10875,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="238" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>27</v>
       </c>
@@ -10929,7 +10913,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="239" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>22</v>
       </c>
@@ -10967,7 +10951,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="240" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>17</v>
       </c>
@@ -11005,7 +10989,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="241" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>20</v>
       </c>
@@ -11043,7 +11027,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="242" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>17</v>
       </c>
@@ -11081,7 +11065,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="243" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>20</v>
       </c>
@@ -11119,7 +11103,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="244" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>32</v>
       </c>
@@ -11157,7 +11141,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="245" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>27</v>
       </c>
@@ -11195,7 +11179,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="246" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>27</v>
       </c>
@@ -11233,7 +11217,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="247" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>22</v>
       </c>
@@ -11271,7 +11255,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="248" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>22</v>
       </c>
@@ -11309,7 +11293,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="249" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>22</v>
       </c>
@@ -11347,7 +11331,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="250" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>17</v>
       </c>
@@ -11385,7 +11369,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="251" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>492</v>
       </c>
@@ -11423,7 +11407,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="252" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>20</v>
       </c>
@@ -11461,7 +11445,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="253" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>32</v>
       </c>
@@ -11499,7 +11483,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="254" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>17</v>
       </c>
@@ -11537,7 +11521,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="255" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>27</v>
       </c>
@@ -11575,7 +11559,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="256" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>22</v>
       </c>
@@ -11613,7 +11597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="257" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>20</v>
       </c>
@@ -11651,7 +11635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>20</v>
       </c>
@@ -11727,7 +11711,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="260" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>24</v>
       </c>
@@ -11765,7 +11749,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="261" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>24</v>
       </c>
@@ -11803,7 +11787,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="262" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>20</v>
       </c>
@@ -11841,7 +11825,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="263" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>27</v>
       </c>
@@ -11879,7 +11863,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="264" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>22</v>
       </c>
@@ -11917,7 +11901,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="265" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>22</v>
       </c>
@@ -11955,7 +11939,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="266" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>27</v>
       </c>
@@ -11993,7 +11977,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="267" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>27</v>
       </c>
@@ -12031,7 +12015,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="268" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>27</v>
       </c>
@@ -12373,7 +12357,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="277" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>27</v>
       </c>
@@ -12411,7 +12395,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="278" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>27</v>
       </c>
@@ -12449,7 +12433,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="279" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>22</v>
       </c>
@@ -12487,7 +12471,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="280" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>24</v>
       </c>
@@ -12525,7 +12509,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="281" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>24</v>
       </c>
@@ -12563,7 +12547,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="282" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>24</v>
       </c>
@@ -12601,7 +12585,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="283" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>24</v>
       </c>
@@ -12639,7 +12623,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="284" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>24</v>
       </c>
@@ -12677,7 +12661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>24</v>
       </c>
@@ -12715,7 +12699,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="286" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>24</v>
       </c>
@@ -12753,7 +12737,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="287" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>24</v>
       </c>
@@ -12791,7 +12775,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="288" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>24</v>
       </c>
@@ -12829,7 +12813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>24</v>
       </c>
@@ -12867,7 +12851,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="290" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>24</v>
       </c>
@@ -12905,7 +12889,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="291" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>24</v>
       </c>
@@ -12943,7 +12927,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="292" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>24</v>
       </c>
@@ -12981,7 +12965,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="293" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>24</v>
       </c>
@@ -13019,7 +13003,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="294" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>24</v>
       </c>
@@ -13057,7 +13041,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="295" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>492</v>
       </c>
@@ -13095,7 +13079,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="296" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>24</v>
       </c>
@@ -13133,7 +13117,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="297" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>24</v>
       </c>
@@ -13171,7 +13155,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="298" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>24</v>
       </c>
@@ -13209,7 +13193,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="299" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>24</v>
       </c>
@@ -13247,7 +13231,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="300" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>20</v>
       </c>
@@ -13285,7 +13269,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="301" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>22</v>
       </c>
@@ -13323,7 +13307,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="302" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>492</v>
       </c>
@@ -13361,7 +13345,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="303" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>17</v>
       </c>
@@ -13399,7 +13383,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="304" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>20</v>
       </c>
@@ -13437,7 +13421,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="305" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>27</v>
       </c>
@@ -13475,7 +13459,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="306" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>27</v>
       </c>
@@ -13513,7 +13497,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="307" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>27</v>
       </c>
@@ -13551,7 +13535,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="308" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>20</v>
       </c>
@@ -13589,7 +13573,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="309" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>20</v>
       </c>
@@ -13627,7 +13611,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="310" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>32</v>
       </c>
@@ -13665,7 +13649,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="311" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>22</v>
       </c>
@@ -13703,7 +13687,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="312" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>17</v>
       </c>
@@ -13741,7 +13725,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="313" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>27</v>
       </c>
@@ -13779,7 +13763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>24</v>
       </c>
@@ -13817,7 +13801,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="315" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>24</v>
       </c>
@@ -13855,7 +13839,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="316" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>492</v>
       </c>
@@ -13893,7 +13877,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="317" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>492</v>
       </c>
@@ -13931,7 +13915,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="318" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>20</v>
       </c>
@@ -13969,7 +13953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>20</v>
       </c>
@@ -14007,7 +13991,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="320" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>20</v>
       </c>
@@ -14045,7 +14029,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="321" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>27</v>
       </c>
@@ -14083,7 +14067,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="322" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>27</v>
       </c>
@@ -14121,7 +14105,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="323" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>27</v>
       </c>
@@ -14159,7 +14143,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="324" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>24</v>
       </c>
@@ -14197,7 +14181,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="325" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>24</v>
       </c>
@@ -14235,7 +14219,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="326" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>17</v>
       </c>
@@ -14273,7 +14257,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="327" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>17</v>
       </c>
@@ -14311,7 +14295,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="328" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>24</v>
       </c>
@@ -14349,7 +14333,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="329" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>24</v>
       </c>
@@ -14387,7 +14371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>492</v>
       </c>
@@ -14425,7 +14409,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="331" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>492</v>
       </c>
@@ -14463,7 +14447,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="332" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>20</v>
       </c>
@@ -14501,7 +14485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>20</v>
       </c>
@@ -14539,7 +14523,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="334" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>20</v>
       </c>
@@ -14577,7 +14561,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="335" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>27</v>
       </c>
@@ -14615,7 +14599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>27</v>
       </c>
@@ -14653,7 +14637,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="337" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>27</v>
       </c>
@@ -14691,7 +14675,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="338" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>24</v>
       </c>
@@ -14729,7 +14713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>24</v>
       </c>
@@ -14767,7 +14751,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="340" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>24</v>
       </c>
@@ -14805,7 +14789,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="341" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>17</v>
       </c>
@@ -14843,7 +14827,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="342" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>17</v>
       </c>
@@ -14881,7 +14865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="343" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>17</v>
       </c>
@@ -14919,7 +14903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>17</v>
       </c>
@@ -14957,7 +14941,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="345" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>492</v>
       </c>
@@ -14995,7 +14979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>24</v>
       </c>
@@ -15033,7 +15017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>492</v>
       </c>
@@ -15071,7 +15055,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="348" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>17</v>
       </c>
@@ -15109,7 +15093,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="349" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>492</v>
       </c>
@@ -15147,7 +15131,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="350" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>32</v>
       </c>
@@ -15185,7 +15169,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="351" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>24</v>
       </c>
@@ -15223,7 +15207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="352" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>24</v>
       </c>
@@ -15261,7 +15245,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="353" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>24</v>
       </c>
@@ -15299,7 +15283,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="354" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>492</v>
       </c>
@@ -15337,7 +15321,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="355" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>24</v>
       </c>
@@ -15375,7 +15359,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="356" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>24</v>
       </c>
@@ -15413,7 +15397,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="357" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>24</v>
       </c>
@@ -15451,7 +15435,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="358" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>24</v>
       </c>
@@ -15489,7 +15473,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="359" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>24</v>
       </c>
@@ -15527,7 +15511,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="360" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>24</v>
       </c>
@@ -15565,7 +15549,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="361" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>24</v>
       </c>
@@ -15603,7 +15587,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="362" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>24</v>
       </c>
@@ -15641,7 +15625,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="363" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>24</v>
       </c>
@@ -15679,7 +15663,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="364" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>24</v>
       </c>
@@ -15717,7 +15701,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="365" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>492</v>
       </c>
@@ -15755,7 +15739,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="366" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>17</v>
       </c>
@@ -15793,7 +15777,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="367" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>24</v>
       </c>
@@ -15831,7 +15815,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="368" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>24</v>
       </c>
@@ -15869,7 +15853,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="369" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>17</v>
       </c>
@@ -15907,7 +15891,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="370" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>492</v>
       </c>
@@ -15945,7 +15929,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="371" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
         <v>27</v>
       </c>
@@ -15983,7 +15967,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="372" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>22</v>
       </c>
@@ -16021,7 +16005,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="373" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>27</v>
       </c>
@@ -16059,7 +16043,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="374" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>32</v>
       </c>
@@ -16097,7 +16081,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="375" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
         <v>22</v>
       </c>
@@ -16135,7 +16119,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="376" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>24</v>
       </c>
@@ -16173,7 +16157,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="377" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>24</v>
       </c>
@@ -16211,7 +16195,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="378" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>492</v>
       </c>
@@ -16249,7 +16233,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="379" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>24</v>
       </c>
@@ -16287,7 +16271,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="380" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>24</v>
       </c>
@@ -16325,7 +16309,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="381" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>492</v>
       </c>
@@ -16363,7 +16347,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="382" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>27</v>
       </c>
@@ -16401,7 +16385,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="383" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>27</v>
       </c>
@@ -16439,7 +16423,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="384" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>27</v>
       </c>
@@ -16477,7 +16461,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="385" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
         <v>27</v>
       </c>
@@ -16515,7 +16499,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="386" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>27</v>
       </c>
@@ -16553,7 +16537,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="387" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
         <v>27</v>
       </c>
@@ -16591,7 +16575,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="388" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
         <v>27</v>
       </c>
@@ -16629,7 +16613,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="389" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
         <v>27</v>
       </c>
@@ -16667,7 +16651,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="390" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>27</v>
       </c>
@@ -16705,7 +16689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="391" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>27</v>
       </c>
@@ -16743,7 +16727,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="392" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
         <v>27</v>
       </c>
@@ -16781,7 +16765,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="393" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>27</v>
       </c>
@@ -16819,7 +16803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="394" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>27</v>
       </c>
@@ -16857,7 +16841,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="395" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>27</v>
       </c>
@@ -16895,7 +16879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="396" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
         <v>492</v>
       </c>
@@ -16933,7 +16917,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="397" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
         <v>492</v>
       </c>
@@ -16971,7 +16955,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="398" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
         <v>492</v>
       </c>
@@ -17009,7 +16993,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="399" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
         <v>492</v>
       </c>
@@ -17047,7 +17031,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="400" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>492</v>
       </c>
@@ -17085,7 +17069,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="401" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>492</v>
       </c>
@@ -17123,7 +17107,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="402" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>492</v>
       </c>
@@ -17161,7 +17145,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="403" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>492</v>
       </c>
@@ -17199,7 +17183,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="404" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
         <v>492</v>
       </c>
@@ -17237,7 +17221,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="405" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
         <v>492</v>
       </c>
@@ -17275,7 +17259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="406" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>20</v>
       </c>
@@ -17313,7 +17297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="407" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
         <v>20</v>
       </c>
@@ -17351,7 +17335,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="408" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
         <v>20</v>
       </c>
@@ -17389,7 +17373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="409" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
         <v>27</v>
       </c>
@@ -17427,7 +17411,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="410" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>27</v>
       </c>
@@ -17465,7 +17449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="411" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
         <v>24</v>
       </c>
@@ -17503,7 +17487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="412" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
         <v>24</v>
       </c>
@@ -17541,7 +17525,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="413" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
         <v>24</v>
       </c>
@@ -17579,7 +17563,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="414" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>17</v>
       </c>
@@ -17617,7 +17601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
         <v>17</v>
       </c>
@@ -17655,7 +17639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="416" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
         <v>24</v>
       </c>
@@ -17693,7 +17677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="417" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
         <v>492</v>
       </c>
@@ -17731,7 +17715,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="418" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
         <v>492</v>
       </c>
@@ -17769,7 +17753,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="419" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
         <v>492</v>
       </c>
@@ -17807,7 +17791,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="420" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
         <v>17</v>
       </c>
@@ -17845,7 +17829,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="421" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
         <v>20</v>
       </c>
@@ -17883,7 +17867,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="422" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
         <v>27</v>
       </c>
@@ -17921,7 +17905,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="423" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
         <v>20</v>
       </c>
@@ -17959,7 +17943,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="424" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
         <v>27</v>
       </c>
@@ -17997,7 +17981,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="425" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
         <v>32</v>
       </c>
@@ -18035,7 +18019,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="426" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
         <v>22</v>
       </c>
@@ -18073,7 +18057,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="427" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
         <v>20</v>
       </c>
@@ -18111,7 +18095,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="428" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
         <v>20</v>
       </c>
@@ -18149,7 +18133,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="429" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
         <v>17</v>
       </c>
@@ -18187,7 +18171,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="430" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
         <v>27</v>
       </c>
@@ -18225,7 +18209,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="431" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
         <v>32</v>
       </c>
@@ -18263,7 +18247,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="432" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
         <v>27</v>
       </c>
@@ -18301,7 +18285,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="433" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
         <v>17</v>
       </c>
@@ -18339,7 +18323,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="434" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
         <v>17</v>
       </c>
@@ -18377,7 +18361,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="435" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
         <v>27</v>
       </c>
@@ -18415,7 +18399,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="436" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
         <v>20</v>
       </c>
@@ -18453,7 +18437,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="437" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
         <v>17</v>
       </c>
@@ -18491,7 +18475,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="438" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
         <v>492</v>
       </c>
@@ -18529,7 +18513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="439" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
         <v>20</v>
       </c>
@@ -18567,7 +18551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="440" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
         <v>27</v>
       </c>
@@ -18605,7 +18589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="441" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
         <v>32</v>
       </c>
@@ -18643,7 +18627,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="442" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
         <v>17</v>
       </c>
@@ -18681,7 +18665,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="443" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
         <v>27</v>
       </c>
@@ -18719,7 +18703,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="444" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
         <v>32</v>
       </c>
@@ -18757,7 +18741,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="445" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
         <v>492</v>
       </c>
@@ -18795,7 +18779,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="446" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
         <v>20</v>
       </c>
@@ -18833,7 +18817,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="447" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
         <v>20</v>
       </c>
@@ -18871,7 +18855,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="448" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
         <v>492</v>
       </c>
@@ -18909,7 +18893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="449" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
         <v>492</v>
       </c>
@@ -18947,7 +18931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="450" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
         <v>492</v>
       </c>
@@ -18985,7 +18969,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="451" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
         <v>20</v>
       </c>
@@ -19023,7 +19007,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="452" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
         <v>32</v>
       </c>
@@ -19061,7 +19045,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="453" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
         <v>27</v>
       </c>
@@ -19099,7 +19083,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="454" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
         <v>22</v>
       </c>
@@ -19137,7 +19121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="455" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
         <v>24</v>
       </c>
@@ -19175,7 +19159,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="456" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
         <v>17</v>
       </c>
@@ -19213,7 +19197,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="457" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
         <v>24</v>
       </c>
@@ -19251,7 +19235,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="458" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
         <v>22</v>
       </c>
@@ -19289,7 +19273,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="459" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
         <v>17</v>
       </c>
@@ -19327,7 +19311,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="460" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
         <v>24</v>
       </c>
@@ -19365,7 +19349,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="461" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
         <v>24</v>
       </c>
@@ -19403,7 +19387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="462" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
         <v>20</v>
       </c>
@@ -19441,7 +19425,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="463" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
         <v>32</v>
       </c>
@@ -19479,7 +19463,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="464" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
         <v>17</v>
       </c>
@@ -19517,7 +19501,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="465" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
         <v>27</v>
       </c>
@@ -19555,7 +19539,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="466" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
         <v>20</v>
       </c>
@@ -19593,7 +19577,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="467" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
         <v>20</v>
       </c>
@@ -19631,7 +19615,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="468" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
         <v>20</v>
       </c>
@@ -19669,7 +19653,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="469" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
         <v>22</v>
       </c>
@@ -19707,7 +19691,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="470" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
         <v>20</v>
       </c>
@@ -19745,7 +19729,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="471" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
         <v>20</v>
       </c>
@@ -19783,7 +19767,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="472" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
         <v>22</v>
       </c>
@@ -19821,7 +19805,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="473" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
         <v>20</v>
       </c>
